--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -3798,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127360220</v>
+        <v>127381942</v>
       </c>
       <c r="B31" t="n">
-        <v>57654</v>
+        <v>79632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,43 +3809,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3853,10 +3836,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560903</v>
+        <v>560617</v>
       </c>
       <c r="R31" t="n">
-        <v>6463535</v>
+        <v>6463688</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3891,17 +3874,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Bebott bohål</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3920,10 +3899,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127360157</v>
+        <v>127381955</v>
       </c>
       <c r="B32" t="n">
-        <v>91346</v>
+        <v>57654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3931,26 +3910,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3958,10 +3950,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560850</v>
+        <v>560617</v>
       </c>
       <c r="R32" t="n">
-        <v>6463569</v>
+        <v>6463688</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3996,13 +3988,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4021,10 +4017,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127381942</v>
+        <v>127360220</v>
       </c>
       <c r="B33" t="n">
-        <v>79632</v>
+        <v>57654</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4032,26 +4028,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4059,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560617</v>
+        <v>560903</v>
       </c>
       <c r="R33" t="n">
-        <v>6463688</v>
+        <v>6463535</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4097,13 +4110,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Bebott bohål</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4122,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127381955</v>
+        <v>127360157</v>
       </c>
       <c r="B34" t="n">
-        <v>57654</v>
+        <v>91346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4133,39 +4150,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4173,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560617</v>
+        <v>560850</v>
       </c>
       <c r="R34" t="n">
-        <v>6463688</v>
+        <v>6463569</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4211,17 +4215,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -776,38 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127359952</v>
+        <v>127360839</v>
       </c>
       <c r="B3" t="n">
-        <v>97149</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2604</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560850</v>
+        <v>560571</v>
       </c>
       <c r="R3" t="n">
-        <v>6463588</v>
+        <v>6463719</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,37 +877,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127360839</v>
+        <v>127359952</v>
       </c>
       <c r="B4" t="n">
-        <v>79632</v>
+        <v>97149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2604</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560571</v>
+        <v>560850</v>
       </c>
       <c r="R4" t="n">
-        <v>6463719</v>
+        <v>6463588</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127355369</v>
+        <v>127355314</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>91745</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,43 +1434,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102977</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1478,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560738</v>
+        <v>560745</v>
       </c>
       <c r="R9" t="n">
-        <v>6463703</v>
+        <v>6463691</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,6 +1505,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1540,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127355314</v>
+        <v>127355369</v>
       </c>
       <c r="B10" t="n">
-        <v>91745</v>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,26 +1535,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5420</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1578,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560745</v>
+        <v>560738</v>
       </c>
       <c r="R10" t="n">
-        <v>6463691</v>
+        <v>6463703</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1622,7 +1623,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127355188</v>
+        <v>127360624</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>57654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,21 +1770,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1800,7 +1800,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560790</v>
+        <v>560704</v>
       </c>
       <c r="R12" t="n">
-        <v>6463749</v>
+        <v>6463675</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Försök till bobygge</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127360624</v>
+        <v>127355188</v>
       </c>
       <c r="B13" t="n">
-        <v>57654</v>
+        <v>57817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1918,7 +1918,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560704</v>
+        <v>560790</v>
       </c>
       <c r="R13" t="n">
-        <v>6463675</v>
+        <v>6463749</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Försök till bobygge</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2108,10 +2108,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127354529</v>
+        <v>127359646</v>
       </c>
       <c r="B15" t="n">
-        <v>91326</v>
+        <v>57654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2119,26 +2119,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2146,10 +2159,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560782</v>
+        <v>560751</v>
       </c>
       <c r="R15" t="n">
-        <v>6463706</v>
+        <v>6463687</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2184,13 +2197,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2209,10 +2226,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127359646</v>
+        <v>127354529</v>
       </c>
       <c r="B16" t="n">
-        <v>57654</v>
+        <v>91326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2220,39 +2237,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2260,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560751</v>
+        <v>560782</v>
       </c>
       <c r="R16" t="n">
-        <v>6463687</v>
+        <v>6463706</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2298,17 +2302,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127360616</v>
+        <v>127359706</v>
       </c>
       <c r="B21" t="n">
-        <v>79632</v>
+        <v>5492</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,26 +2785,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2812,10 +2814,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560704</v>
+        <v>560830</v>
       </c>
       <c r="R21" t="n">
-        <v>6463675</v>
+        <v>6463638</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2875,10 +2877,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127359706</v>
+        <v>127360616</v>
       </c>
       <c r="B22" t="n">
-        <v>5492</v>
+        <v>79632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2886,28 +2888,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560830</v>
+        <v>560704</v>
       </c>
       <c r="R22" t="n">
-        <v>6463638</v>
+        <v>6463675</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127381942</v>
+        <v>127360220</v>
       </c>
       <c r="B31" t="n">
-        <v>79632</v>
+        <v>57654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,26 +3809,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3836,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560617</v>
+        <v>560903</v>
       </c>
       <c r="R31" t="n">
-        <v>6463688</v>
+        <v>6463535</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3874,13 +3891,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Bebott bohål</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4017,10 +4038,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127360220</v>
+        <v>127381942</v>
       </c>
       <c r="B33" t="n">
-        <v>57654</v>
+        <v>79632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4028,43 +4049,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4072,10 +4076,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560903</v>
+        <v>560617</v>
       </c>
       <c r="R33" t="n">
-        <v>6463535</v>
+        <v>6463688</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4110,17 +4114,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Bebott bohål</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4544,10 +4544,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127359873</v>
+        <v>127354580</v>
       </c>
       <c r="B38" t="n">
-        <v>91346</v>
+        <v>57654</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,26 +4555,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4582,10 +4595,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560879</v>
+        <v>560782</v>
       </c>
       <c r="R38" t="n">
-        <v>6463611</v>
+        <v>6463706</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4620,13 +4633,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4645,10 +4662,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127354580</v>
+        <v>127359873</v>
       </c>
       <c r="B39" t="n">
-        <v>57654</v>
+        <v>91346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4656,39 +4673,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4696,10 +4700,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560782</v>
+        <v>560879</v>
       </c>
       <c r="R39" t="n">
-        <v>6463706</v>
+        <v>6463611</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4734,17 +4738,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4880,7 +4880,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127381965</v>
+        <v>127355339</v>
       </c>
       <c r="B41" t="n">
         <v>57654</v>
@@ -4918,7 +4918,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4931,10 +4935,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>560624</v>
+        <v>560745</v>
       </c>
       <c r="R41" t="n">
-        <v>6463737</v>
+        <v>6463691</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4971,7 +4975,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4998,7 +5002,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127355339</v>
+        <v>127360701</v>
       </c>
       <c r="B42" t="n">
         <v>57654</v>
@@ -5036,14 +5040,10 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>560745</v>
+        <v>560662</v>
       </c>
       <c r="R42" t="n">
-        <v>6463691</v>
+        <v>6463677</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5120,7 +5120,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127360701</v>
+        <v>127381965</v>
       </c>
       <c r="B43" t="n">
         <v>57654</v>
@@ -5161,7 +5161,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560662</v>
+        <v>560624</v>
       </c>
       <c r="R43" t="n">
-        <v>6463677</v>
+        <v>6463737</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -4240,37 +4240,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127354652</v>
+        <v>127360190</v>
       </c>
       <c r="B35" t="n">
-        <v>91346</v>
+        <v>96046</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4278,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560773</v>
+        <v>560897</v>
       </c>
       <c r="R35" t="n">
-        <v>6463729</v>
+        <v>6463507</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4341,10 +4342,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127355375</v>
+        <v>127354652</v>
       </c>
       <c r="B36" t="n">
-        <v>79632</v>
+        <v>91346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4352,21 +4353,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4379,10 +4380,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560738</v>
+        <v>560773</v>
       </c>
       <c r="R36" t="n">
-        <v>6463703</v>
+        <v>6463729</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4442,38 +4443,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127360190</v>
+        <v>127355375</v>
       </c>
       <c r="B37" t="n">
-        <v>96046</v>
+        <v>79632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560897</v>
+        <v>560738</v>
       </c>
       <c r="R37" t="n">
-        <v>6463507</v>
+        <v>6463703</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -776,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127360839</v>
+        <v>127359952</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>97149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>2604</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -814,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560571</v>
+        <v>560850</v>
       </c>
       <c r="R3" t="n">
-        <v>6463719</v>
+        <v>6463588</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,38 +878,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127359952</v>
+        <v>127360839</v>
       </c>
       <c r="B4" t="n">
-        <v>97149</v>
+        <v>79632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2604</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560850</v>
+        <v>560571</v>
       </c>
       <c r="R4" t="n">
-        <v>6463588</v>
+        <v>6463719</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127359680</v>
+        <v>127354262</v>
       </c>
       <c r="B24" t="n">
-        <v>91346</v>
+        <v>57654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,26 +3090,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3117,10 +3130,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560809</v>
+        <v>560850</v>
       </c>
       <c r="R24" t="n">
-        <v>6463646</v>
+        <v>6463659</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3161,7 +3174,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3180,10 +3192,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127360466</v>
+        <v>127359680</v>
       </c>
       <c r="B25" t="n">
-        <v>79632</v>
+        <v>91346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,21 +3203,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3218,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560882</v>
+        <v>560809</v>
       </c>
       <c r="R25" t="n">
-        <v>6463540</v>
+        <v>6463646</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3281,10 +3293,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127355274</v>
+        <v>127360466</v>
       </c>
       <c r="B26" t="n">
-        <v>91346</v>
+        <v>79632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3292,21 +3304,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3319,10 +3331,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560763</v>
+        <v>560882</v>
       </c>
       <c r="R26" t="n">
-        <v>6463697</v>
+        <v>6463540</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3382,10 +3394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127354262</v>
+        <v>127355274</v>
       </c>
       <c r="B27" t="n">
-        <v>57654</v>
+        <v>91346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3393,39 +3405,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3433,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560850</v>
+        <v>560763</v>
       </c>
       <c r="R27" t="n">
-        <v>6463659</v>
+        <v>6463697</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3477,6 +3476,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4240,38 +4240,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127360190</v>
+        <v>127354652</v>
       </c>
       <c r="B35" t="n">
-        <v>96046</v>
+        <v>91346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4279,10 +4278,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560897</v>
+        <v>560773</v>
       </c>
       <c r="R35" t="n">
-        <v>6463507</v>
+        <v>6463729</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4342,10 +4341,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127354652</v>
+        <v>127355375</v>
       </c>
       <c r="B36" t="n">
-        <v>91346</v>
+        <v>79632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4353,21 +4352,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4380,10 +4379,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560773</v>
+        <v>560738</v>
       </c>
       <c r="R36" t="n">
-        <v>6463729</v>
+        <v>6463703</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4443,37 +4442,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127355375</v>
+        <v>127360190</v>
       </c>
       <c r="B37" t="n">
-        <v>79632</v>
+        <v>96046</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560738</v>
+        <v>560897</v>
       </c>
       <c r="R37" t="n">
-        <v>6463703</v>
+        <v>6463507</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127355252</v>
       </c>
       <c r="B2" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127359952</v>
       </c>
       <c r="B3" t="n">
-        <v>97149</v>
+        <v>97153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127360839</v>
       </c>
       <c r="B4" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>127355282</v>
       </c>
       <c r="B5" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127359945</v>
       </c>
       <c r="B6" t="n">
-        <v>97123</v>
+        <v>97127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>127354741</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>127355148</v>
       </c>
       <c r="B8" t="n">
-        <v>57670</v>
+        <v>57674</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>127355314</v>
       </c>
       <c r="B9" t="n">
-        <v>91745</v>
+        <v>91749</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>127355369</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>57655</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>127359896</v>
       </c>
       <c r="B11" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127360624</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>127355188</v>
       </c>
       <c r="B13" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127360820</v>
+        <v>127354529</v>
       </c>
       <c r="B14" t="n">
-        <v>57654</v>
+        <v>91330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,39 +2006,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2046,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560582</v>
+        <v>560782</v>
       </c>
       <c r="R14" t="n">
-        <v>6463723</v>
+        <v>6463706</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2090,6 +2077,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2108,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127359646</v>
+        <v>127360820</v>
       </c>
       <c r="B15" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2149,7 +2137,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2159,10 +2147,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560751</v>
+        <v>560582</v>
       </c>
       <c r="R15" t="n">
-        <v>6463687</v>
+        <v>6463723</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2195,11 +2183,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2226,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127354529</v>
+        <v>127359646</v>
       </c>
       <c r="B16" t="n">
-        <v>91326</v>
+        <v>57658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,26 +2220,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2264,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560782</v>
+        <v>560751</v>
       </c>
       <c r="R16" t="n">
-        <v>6463706</v>
+        <v>6463687</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2302,13 +2298,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127355403</v>
+        <v>127359699</v>
       </c>
       <c r="B17" t="n">
-        <v>57654</v>
+        <v>91350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,39 +2338,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2378,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560738</v>
+        <v>560825</v>
       </c>
       <c r="R17" t="n">
-        <v>6463703</v>
+        <v>6463632</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2418,7 +2405,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Flera på samma träd</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2427,6 +2414,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2445,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127359702</v>
+        <v>127355403</v>
       </c>
       <c r="B18" t="n">
-        <v>79632</v>
+        <v>57658</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,26 +2444,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2483,10 +2484,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560825</v>
+        <v>560738</v>
       </c>
       <c r="R18" t="n">
-        <v>6463632</v>
+        <v>6463703</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2521,13 +2522,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2546,10 +2551,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127359699</v>
+        <v>127359702</v>
       </c>
       <c r="B19" t="n">
-        <v>91346</v>
+        <v>79636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2557,21 +2562,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2622,11 +2627,6 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Flera på samma träd</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127382193</v>
+        <v>127359706</v>
       </c>
       <c r="B20" t="n">
-        <v>57654</v>
+        <v>5493</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,43 +2663,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>101410</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2707,10 +2692,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560809</v>
+        <v>560830</v>
       </c>
       <c r="R20" t="n">
-        <v>6463640</v>
+        <v>6463638</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2745,17 +2730,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Observerad</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2774,10 +2755,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127359706</v>
+        <v>127382193</v>
       </c>
       <c r="B21" t="n">
-        <v>5492</v>
+        <v>57658</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,28 +2766,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101410</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2814,10 +2810,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560830</v>
+        <v>560809</v>
       </c>
       <c r="R21" t="n">
-        <v>6463638</v>
+        <v>6463640</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2852,13 +2848,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Observerad</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>127360616</v>
       </c>
       <c r="B22" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>127359577</v>
       </c>
       <c r="B23" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>127354262</v>
       </c>
       <c r="B24" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>127359680</v>
       </c>
       <c r="B25" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3293,10 +3293,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127360466</v>
+        <v>127355274</v>
       </c>
       <c r="B26" t="n">
-        <v>79632</v>
+        <v>91350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3304,21 +3304,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560882</v>
+        <v>560763</v>
       </c>
       <c r="R26" t="n">
-        <v>6463540</v>
+        <v>6463697</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3394,10 +3394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127355274</v>
+        <v>127360466</v>
       </c>
       <c r="B27" t="n">
-        <v>91346</v>
+        <v>79636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3405,21 +3405,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560763</v>
+        <v>560882</v>
       </c>
       <c r="R27" t="n">
-        <v>6463697</v>
+        <v>6463540</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3498,7 +3498,7 @@
         <v>127360687</v>
       </c>
       <c r="B28" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,32 +3596,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127359655</v>
+        <v>127359663</v>
       </c>
       <c r="B29" t="n">
-        <v>79100</v>
+        <v>91350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6450</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560751</v>
+        <v>560780</v>
       </c>
       <c r="R29" t="n">
-        <v>6463687</v>
+        <v>6463653</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127359663</v>
+        <v>127359655</v>
       </c>
       <c r="B30" t="n">
-        <v>91346</v>
+        <v>79104</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6450</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560780</v>
+        <v>560751</v>
       </c>
       <c r="R30" t="n">
-        <v>6463653</v>
+        <v>6463687</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3801,7 +3801,7 @@
         <v>127360220</v>
       </c>
       <c r="B31" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>127381955</v>
       </c>
       <c r="B32" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>127381942</v>
       </c>
       <c r="B33" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>127360157</v>
       </c>
       <c r="B34" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>127354652</v>
       </c>
       <c r="B35" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4341,37 +4341,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127355375</v>
+        <v>127360190</v>
       </c>
       <c r="B36" t="n">
-        <v>79632</v>
+        <v>96050</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4379,10 +4380,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560738</v>
+        <v>560897</v>
       </c>
       <c r="R36" t="n">
-        <v>6463703</v>
+        <v>6463507</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4442,38 +4443,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127360190</v>
+        <v>127355375</v>
       </c>
       <c r="B37" t="n">
-        <v>96046</v>
+        <v>79636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560897</v>
+        <v>560738</v>
       </c>
       <c r="R37" t="n">
-        <v>6463507</v>
+        <v>6463703</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4544,10 +4544,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127354580</v>
+        <v>127359873</v>
       </c>
       <c r="B38" t="n">
-        <v>57654</v>
+        <v>91350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,39 +4555,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4595,10 +4582,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560782</v>
+        <v>560879</v>
       </c>
       <c r="R38" t="n">
-        <v>6463706</v>
+        <v>6463611</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4633,17 +4620,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4662,10 +4645,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127359873</v>
+        <v>127354580</v>
       </c>
       <c r="B39" t="n">
-        <v>91346</v>
+        <v>57658</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4673,26 +4656,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4700,10 +4696,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560879</v>
+        <v>560782</v>
       </c>
       <c r="R39" t="n">
-        <v>6463611</v>
+        <v>6463706</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4738,13 +4734,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4766,7 +4766,7 @@
         <v>127360176</v>
       </c>
       <c r="B40" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4880,10 +4880,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127355339</v>
+        <v>127360121</v>
       </c>
       <c r="B41" t="n">
-        <v>57654</v>
+        <v>57674</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4891,16 +4891,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4918,11 +4918,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4935,10 +4931,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>560745</v>
+        <v>560850</v>
       </c>
       <c r="R41" t="n">
-        <v>6463691</v>
+        <v>6463588</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4975,7 +4971,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Bohål, troligen mindre hackspett (ev större)</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5002,10 +4998,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127360701</v>
+        <v>127360842</v>
       </c>
       <c r="B42" t="n">
-        <v>57654</v>
+        <v>91350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5013,39 +5009,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5053,10 +5036,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>560662</v>
+        <v>560551</v>
       </c>
       <c r="R42" t="n">
-        <v>6463677</v>
+        <v>6463735</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5091,17 +5074,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5120,10 +5099,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127381965</v>
+        <v>127355339</v>
       </c>
       <c r="B43" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5158,7 +5137,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -5171,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560624</v>
+        <v>560745</v>
       </c>
       <c r="R43" t="n">
-        <v>6463737</v>
+        <v>6463691</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5211,7 +5194,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5238,10 +5221,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127360121</v>
+        <v>127360701</v>
       </c>
       <c r="B44" t="n">
-        <v>57670</v>
+        <v>57658</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5249,16 +5232,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5279,7 +5262,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5289,10 +5272,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560850</v>
+        <v>560662</v>
       </c>
       <c r="R44" t="n">
-        <v>6463588</v>
+        <v>6463677</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5329,7 +5312,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Bohål, troligen mindre hackspett (ev större)</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5356,10 +5339,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127360842</v>
+        <v>127381965</v>
       </c>
       <c r="B45" t="n">
-        <v>91346</v>
+        <v>57658</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5367,26 +5350,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5394,10 +5390,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560551</v>
+        <v>560624</v>
       </c>
       <c r="R45" t="n">
-        <v>6463735</v>
+        <v>6463737</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5432,13 +5428,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -776,38 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127359952</v>
+        <v>127360839</v>
       </c>
       <c r="B3" t="n">
-        <v>97153</v>
+        <v>79636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2604</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560850</v>
+        <v>560571</v>
       </c>
       <c r="R3" t="n">
-        <v>6463588</v>
+        <v>6463719</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,37 +877,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127360839</v>
+        <v>127359952</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>97153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2604</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560571</v>
+        <v>560850</v>
       </c>
       <c r="R4" t="n">
-        <v>6463719</v>
+        <v>6463588</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127354741</v>
+        <v>127355148</v>
       </c>
       <c r="B7" t="n">
-        <v>57658</v>
+        <v>57674</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1221,7 +1221,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -1234,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560773</v>
+        <v>560778</v>
       </c>
       <c r="R7" t="n">
-        <v>6463729</v>
+        <v>6463736</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1274,7 +1278,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Nyligen använt bo för häckning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127355148</v>
+        <v>127354741</v>
       </c>
       <c r="B8" t="n">
-        <v>57674</v>
+        <v>57658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,16 +1316,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1339,11 +1343,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560778</v>
+        <v>560773</v>
       </c>
       <c r="R8" t="n">
-        <v>6463736</v>
+        <v>6463729</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Nyligen använt bo för häckning.</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127355314</v>
+        <v>127355369</v>
       </c>
       <c r="B9" t="n">
-        <v>91749</v>
+        <v>57655</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,26 +1434,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>102977</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1461,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560745</v>
+        <v>560738</v>
       </c>
       <c r="R9" t="n">
-        <v>6463691</v>
+        <v>6463703</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,7 +1522,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1524,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127355369</v>
+        <v>127355314</v>
       </c>
       <c r="B10" t="n">
-        <v>57655</v>
+        <v>91749</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1535,43 +1551,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102977</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1579,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560738</v>
+        <v>560745</v>
       </c>
       <c r="R10" t="n">
-        <v>6463703</v>
+        <v>6463691</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1623,6 +1622,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1641,7 +1641,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127359896</v>
+        <v>127360624</v>
       </c>
       <c r="B11" t="n">
         <v>57658</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560854</v>
+        <v>560704</v>
       </c>
       <c r="R11" t="n">
-        <v>6463597</v>
+        <v>6463675</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,7 +1759,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127360624</v>
+        <v>127359896</v>
       </c>
       <c r="B12" t="n">
         <v>57658</v>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560704</v>
+        <v>560854</v>
       </c>
       <c r="R12" t="n">
-        <v>6463675</v>
+        <v>6463597</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2433,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127355403</v>
+        <v>127359702</v>
       </c>
       <c r="B18" t="n">
-        <v>57658</v>
+        <v>79636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2444,39 +2444,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2484,10 +2471,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560738</v>
+        <v>560825</v>
       </c>
       <c r="R18" t="n">
-        <v>6463703</v>
+        <v>6463632</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2522,17 +2509,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2551,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127359702</v>
+        <v>127355403</v>
       </c>
       <c r="B19" t="n">
-        <v>79636</v>
+        <v>57658</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,26 +2545,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2589,10 +2585,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560825</v>
+        <v>560738</v>
       </c>
       <c r="R19" t="n">
-        <v>6463632</v>
+        <v>6463703</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2627,13 +2623,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127359706</v>
+        <v>127360616</v>
       </c>
       <c r="B20" t="n">
-        <v>5493</v>
+        <v>79636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,28 +2663,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2692,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560830</v>
+        <v>560704</v>
       </c>
       <c r="R20" t="n">
-        <v>6463638</v>
+        <v>6463675</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2755,10 +2753,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127382193</v>
+        <v>127359706</v>
       </c>
       <c r="B21" t="n">
-        <v>57658</v>
+        <v>5493</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2766,43 +2764,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>101410</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2810,10 +2793,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560809</v>
+        <v>560830</v>
       </c>
       <c r="R21" t="n">
-        <v>6463640</v>
+        <v>6463638</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2848,17 +2831,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Observerad</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2877,10 +2856,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127360616</v>
+        <v>127382193</v>
       </c>
       <c r="B22" t="n">
-        <v>79636</v>
+        <v>57658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2888,26 +2867,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2915,10 +2911,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560704</v>
+        <v>560809</v>
       </c>
       <c r="R22" t="n">
-        <v>6463675</v>
+        <v>6463640</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2953,13 +2949,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Observerad</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3192,7 +3192,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127359680</v>
+        <v>127355274</v>
       </c>
       <c r="B25" t="n">
         <v>91350</v>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560809</v>
+        <v>560763</v>
       </c>
       <c r="R25" t="n">
-        <v>6463646</v>
+        <v>6463697</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127355274</v>
+        <v>127359680</v>
       </c>
       <c r="B26" t="n">
         <v>91350</v>
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560763</v>
+        <v>560809</v>
       </c>
       <c r="R26" t="n">
-        <v>6463697</v>
+        <v>6463646</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3495,10 +3495,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127360687</v>
+        <v>127359663</v>
       </c>
       <c r="B28" t="n">
-        <v>79636</v>
+        <v>91350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3506,21 +3506,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560662</v>
+        <v>560780</v>
       </c>
       <c r="R28" t="n">
-        <v>6463677</v>
+        <v>6463653</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127359663</v>
+        <v>127360687</v>
       </c>
       <c r="B29" t="n">
-        <v>91350</v>
+        <v>79636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560780</v>
+        <v>560662</v>
       </c>
       <c r="R29" t="n">
-        <v>6463653</v>
+        <v>6463677</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127360220</v>
+        <v>127381942</v>
       </c>
       <c r="B31" t="n">
-        <v>57658</v>
+        <v>79636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,43 +3809,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3853,10 +3836,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560903</v>
+        <v>560617</v>
       </c>
       <c r="R31" t="n">
-        <v>6463535</v>
+        <v>6463688</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3891,17 +3874,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Bebott bohål</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3920,7 +3899,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127381955</v>
+        <v>127360220</v>
       </c>
       <c r="B32" t="n">
         <v>57658</v>
@@ -3958,7 +3937,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -3971,10 +3954,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560617</v>
+        <v>560903</v>
       </c>
       <c r="R32" t="n">
-        <v>6463688</v>
+        <v>6463535</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4011,7 +3994,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Bebott bohål</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4038,10 +4021,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127381942</v>
+        <v>127381955</v>
       </c>
       <c r="B33" t="n">
-        <v>79636</v>
+        <v>57658</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4049,26 +4032,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4114,13 +4110,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4341,38 +4341,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127360190</v>
+        <v>127355375</v>
       </c>
       <c r="B36" t="n">
-        <v>96050</v>
+        <v>79636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4380,10 +4379,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560897</v>
+        <v>560738</v>
       </c>
       <c r="R36" t="n">
-        <v>6463507</v>
+        <v>6463703</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4443,37 +4442,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127355375</v>
+        <v>127360190</v>
       </c>
       <c r="B37" t="n">
-        <v>79636</v>
+        <v>96050</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560738</v>
+        <v>560897</v>
       </c>
       <c r="R37" t="n">
-        <v>6463703</v>
+        <v>6463507</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4880,10 +4880,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127360121</v>
+        <v>127360842</v>
       </c>
       <c r="B41" t="n">
-        <v>57674</v>
+        <v>91350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4891,39 +4891,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100048</v>
+        <v>5442</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4931,10 +4918,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>560850</v>
+        <v>560551</v>
       </c>
       <c r="R41" t="n">
-        <v>6463588</v>
+        <v>6463735</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4969,17 +4956,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Bohål, troligen mindre hackspett (ev större)</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4998,10 +4981,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127360842</v>
+        <v>127381965</v>
       </c>
       <c r="B42" t="n">
-        <v>91350</v>
+        <v>57658</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5009,26 +4992,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5036,10 +5032,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>560551</v>
+        <v>560624</v>
       </c>
       <c r="R42" t="n">
-        <v>6463735</v>
+        <v>6463737</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5074,13 +5070,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5221,10 +5221,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127360701</v>
+        <v>127360121</v>
       </c>
       <c r="B44" t="n">
-        <v>57658</v>
+        <v>57674</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5232,16 +5232,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5262,7 +5262,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5272,10 +5272,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560662</v>
+        <v>560850</v>
       </c>
       <c r="R44" t="n">
-        <v>6463677</v>
+        <v>6463588</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Bohål, troligen mindre hackspett (ev större)</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5339,7 +5339,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127381965</v>
+        <v>127360701</v>
       </c>
       <c r="B45" t="n">
         <v>57658</v>
@@ -5380,7 +5380,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560624</v>
+        <v>560662</v>
       </c>
       <c r="R45" t="n">
-        <v>6463737</v>
+        <v>6463677</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127355369</v>
+        <v>127355314</v>
       </c>
       <c r="B9" t="n">
-        <v>57655</v>
+        <v>91749</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,43 +1434,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102977</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1478,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560738</v>
+        <v>560745</v>
       </c>
       <c r="R9" t="n">
-        <v>6463703</v>
+        <v>6463691</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,6 +1505,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1540,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127355314</v>
+        <v>127355369</v>
       </c>
       <c r="B10" t="n">
-        <v>91749</v>
+        <v>57655</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,26 +1535,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5420</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1578,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560745</v>
+        <v>560738</v>
       </c>
       <c r="R10" t="n">
-        <v>6463691</v>
+        <v>6463703</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1622,7 +1623,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127354529</v>
+        <v>127360820</v>
       </c>
       <c r="B14" t="n">
-        <v>91330</v>
+        <v>57658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,26 +2006,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2033,10 +2046,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560782</v>
+        <v>560582</v>
       </c>
       <c r="R14" t="n">
-        <v>6463706</v>
+        <v>6463723</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2077,7 +2090,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2096,7 +2108,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127360820</v>
+        <v>127359646</v>
       </c>
       <c r="B15" t="n">
         <v>57658</v>
@@ -2137,7 +2149,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2147,10 +2159,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560582</v>
+        <v>560751</v>
       </c>
       <c r="R15" t="n">
-        <v>6463723</v>
+        <v>6463687</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2183,6 +2195,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,10 +2226,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127359646</v>
+        <v>127354529</v>
       </c>
       <c r="B16" t="n">
-        <v>57658</v>
+        <v>91330</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2220,39 +2237,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2260,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560751</v>
+        <v>560782</v>
       </c>
       <c r="R16" t="n">
-        <v>6463687</v>
+        <v>6463706</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2298,17 +2302,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127360616</v>
+        <v>127382193</v>
       </c>
       <c r="B20" t="n">
-        <v>79636</v>
+        <v>57658</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,26 +2663,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2690,10 +2707,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560704</v>
+        <v>560809</v>
       </c>
       <c r="R20" t="n">
-        <v>6463675</v>
+        <v>6463640</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2728,13 +2745,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Observerad</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2856,10 +2877,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127382193</v>
+        <v>127360616</v>
       </c>
       <c r="B22" t="n">
-        <v>57658</v>
+        <v>79636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2867,43 +2888,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2911,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560809</v>
+        <v>560704</v>
       </c>
       <c r="R22" t="n">
-        <v>6463640</v>
+        <v>6463675</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2949,17 +2953,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Observerad</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127354262</v>
+        <v>127360466</v>
       </c>
       <c r="B24" t="n">
-        <v>57658</v>
+        <v>79636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,39 +3090,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3130,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560850</v>
+        <v>560882</v>
       </c>
       <c r="R24" t="n">
-        <v>6463659</v>
+        <v>6463540</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3174,6 +3161,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3192,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127355274</v>
+        <v>127354262</v>
       </c>
       <c r="B25" t="n">
-        <v>91350</v>
+        <v>57658</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3203,26 +3191,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3230,10 +3231,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560763</v>
+        <v>560850</v>
       </c>
       <c r="R25" t="n">
-        <v>6463697</v>
+        <v>6463659</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3274,7 +3275,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127359680</v>
+        <v>127355274</v>
       </c>
       <c r="B26" t="n">
         <v>91350</v>
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560809</v>
+        <v>560763</v>
       </c>
       <c r="R26" t="n">
-        <v>6463646</v>
+        <v>6463697</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3394,10 +3394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127360466</v>
+        <v>127359680</v>
       </c>
       <c r="B27" t="n">
-        <v>79636</v>
+        <v>91350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3405,21 +3405,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560882</v>
+        <v>560809</v>
       </c>
       <c r="R27" t="n">
-        <v>6463540</v>
+        <v>6463646</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127381942</v>
+        <v>127360157</v>
       </c>
       <c r="B31" t="n">
-        <v>79636</v>
+        <v>91350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,21 +3809,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560617</v>
+        <v>560850</v>
       </c>
       <c r="R31" t="n">
-        <v>6463688</v>
+        <v>6463569</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127360220</v>
+        <v>127381942</v>
       </c>
       <c r="B32" t="n">
-        <v>57658</v>
+        <v>79636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,43 +3910,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3954,10 +3937,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560903</v>
+        <v>560617</v>
       </c>
       <c r="R32" t="n">
-        <v>6463535</v>
+        <v>6463688</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3992,17 +3975,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Bebott bohål</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4021,7 +4000,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127381955</v>
+        <v>127360220</v>
       </c>
       <c r="B33" t="n">
         <v>57658</v>
@@ -4059,7 +4038,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4072,10 +4055,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560617</v>
+        <v>560903</v>
       </c>
       <c r="R33" t="n">
-        <v>6463688</v>
+        <v>6463535</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4112,7 +4095,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Bebott bohål</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4139,10 +4122,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127360157</v>
+        <v>127381955</v>
       </c>
       <c r="B34" t="n">
-        <v>91350</v>
+        <v>57658</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4150,26 +4133,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4177,10 +4173,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560850</v>
+        <v>560617</v>
       </c>
       <c r="R34" t="n">
-        <v>6463569</v>
+        <v>6463688</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4215,13 +4211,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4240,37 +4240,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127354652</v>
+        <v>127360190</v>
       </c>
       <c r="B35" t="n">
-        <v>91350</v>
+        <v>96050</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4278,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560773</v>
+        <v>560897</v>
       </c>
       <c r="R35" t="n">
-        <v>6463729</v>
+        <v>6463507</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4341,10 +4342,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127355375</v>
+        <v>127354652</v>
       </c>
       <c r="B36" t="n">
-        <v>79636</v>
+        <v>91350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4352,21 +4353,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4379,10 +4380,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560738</v>
+        <v>560773</v>
       </c>
       <c r="R36" t="n">
-        <v>6463703</v>
+        <v>6463729</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4442,38 +4443,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127360190</v>
+        <v>127355375</v>
       </c>
       <c r="B37" t="n">
-        <v>96050</v>
+        <v>79636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560897</v>
+        <v>560738</v>
       </c>
       <c r="R37" t="n">
-        <v>6463507</v>
+        <v>6463703</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -776,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127360839</v>
+        <v>127359952</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>97153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>2604</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -814,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560571</v>
+        <v>560850</v>
       </c>
       <c r="R3" t="n">
-        <v>6463719</v>
+        <v>6463588</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,38 +878,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127359952</v>
+        <v>127360839</v>
       </c>
       <c r="B4" t="n">
-        <v>97153</v>
+        <v>79636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2604</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560850</v>
+        <v>560571</v>
       </c>
       <c r="R4" t="n">
-        <v>6463588</v>
+        <v>6463719</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127355314</v>
+        <v>127355369</v>
       </c>
       <c r="B9" t="n">
-        <v>91749</v>
+        <v>57655</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,26 +1434,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>102977</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1461,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560745</v>
+        <v>560738</v>
       </c>
       <c r="R9" t="n">
-        <v>6463691</v>
+        <v>6463703</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,7 +1522,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1524,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127355369</v>
+        <v>127355314</v>
       </c>
       <c r="B10" t="n">
-        <v>57655</v>
+        <v>91749</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1535,43 +1551,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102977</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1579,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560738</v>
+        <v>560745</v>
       </c>
       <c r="R10" t="n">
-        <v>6463703</v>
+        <v>6463691</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1623,6 +1622,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127360820</v>
+        <v>127354529</v>
       </c>
       <c r="B14" t="n">
-        <v>57658</v>
+        <v>91330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,39 +2006,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2046,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560582</v>
+        <v>560782</v>
       </c>
       <c r="R14" t="n">
-        <v>6463723</v>
+        <v>6463706</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2090,6 +2077,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2108,7 +2096,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127359646</v>
+        <v>127360820</v>
       </c>
       <c r="B15" t="n">
         <v>57658</v>
@@ -2149,7 +2137,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2159,10 +2147,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560751</v>
+        <v>560582</v>
       </c>
       <c r="R15" t="n">
-        <v>6463687</v>
+        <v>6463723</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2195,11 +2183,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2226,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127354529</v>
+        <v>127359646</v>
       </c>
       <c r="B16" t="n">
-        <v>91330</v>
+        <v>57658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,26 +2220,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2264,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560782</v>
+        <v>560751</v>
       </c>
       <c r="R16" t="n">
-        <v>6463706</v>
+        <v>6463687</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2302,13 +2298,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127360466</v>
+        <v>127354262</v>
       </c>
       <c r="B24" t="n">
-        <v>79636</v>
+        <v>57658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,26 +3090,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3117,10 +3130,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560882</v>
+        <v>560850</v>
       </c>
       <c r="R24" t="n">
-        <v>6463540</v>
+        <v>6463659</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3161,7 +3174,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3180,10 +3192,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127354262</v>
+        <v>127355274</v>
       </c>
       <c r="B25" t="n">
-        <v>57658</v>
+        <v>91350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,39 +3203,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3231,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560850</v>
+        <v>560763</v>
       </c>
       <c r="R25" t="n">
-        <v>6463659</v>
+        <v>6463697</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3275,6 +3274,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127355274</v>
+        <v>127359680</v>
       </c>
       <c r="B26" t="n">
         <v>91350</v>
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560763</v>
+        <v>560809</v>
       </c>
       <c r="R26" t="n">
-        <v>6463697</v>
+        <v>6463646</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3394,10 +3394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127359680</v>
+        <v>127360466</v>
       </c>
       <c r="B27" t="n">
-        <v>91350</v>
+        <v>79636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3405,21 +3405,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560809</v>
+        <v>560882</v>
       </c>
       <c r="R27" t="n">
-        <v>6463646</v>
+        <v>6463540</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127360157</v>
+        <v>127381942</v>
       </c>
       <c r="B31" t="n">
-        <v>91350</v>
+        <v>79636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,21 +3809,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560850</v>
+        <v>560617</v>
       </c>
       <c r="R31" t="n">
-        <v>6463569</v>
+        <v>6463688</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127381942</v>
+        <v>127360220</v>
       </c>
       <c r="B32" t="n">
-        <v>79636</v>
+        <v>57658</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,26 +3910,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3937,10 +3954,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560617</v>
+        <v>560903</v>
       </c>
       <c r="R32" t="n">
-        <v>6463688</v>
+        <v>6463535</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3975,13 +3992,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Bebott bohål</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4000,7 +4021,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127360220</v>
+        <v>127381955</v>
       </c>
       <c r="B33" t="n">
         <v>57658</v>
@@ -4038,11 +4059,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4055,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560903</v>
+        <v>560617</v>
       </c>
       <c r="R33" t="n">
-        <v>6463535</v>
+        <v>6463688</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4095,7 +4112,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Bebott bohål</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4122,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127381955</v>
+        <v>127360157</v>
       </c>
       <c r="B34" t="n">
-        <v>57658</v>
+        <v>91350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4133,39 +4150,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4173,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560617</v>
+        <v>560850</v>
       </c>
       <c r="R34" t="n">
-        <v>6463688</v>
+        <v>6463569</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4211,17 +4215,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4240,38 +4240,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127360190</v>
+        <v>127354652</v>
       </c>
       <c r="B35" t="n">
-        <v>96050</v>
+        <v>91350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4279,10 +4278,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560897</v>
+        <v>560773</v>
       </c>
       <c r="R35" t="n">
-        <v>6463507</v>
+        <v>6463729</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4342,10 +4341,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127354652</v>
+        <v>127355375</v>
       </c>
       <c r="B36" t="n">
-        <v>91350</v>
+        <v>79636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4353,21 +4352,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4380,10 +4379,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560773</v>
+        <v>560738</v>
       </c>
       <c r="R36" t="n">
-        <v>6463729</v>
+        <v>6463703</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4443,37 +4442,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127355375</v>
+        <v>127360190</v>
       </c>
       <c r="B37" t="n">
-        <v>79636</v>
+        <v>96050</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560738</v>
+        <v>560897</v>
       </c>
       <c r="R37" t="n">
-        <v>6463703</v>
+        <v>6463507</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -982,7 +982,7 @@
         <v>127355282</v>
       </c>
       <c r="B5" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127355148</v>
+        <v>127354741</v>
       </c>
       <c r="B7" t="n">
-        <v>57674</v>
+        <v>57658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1221,11 +1221,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -1238,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560778</v>
+        <v>560773</v>
       </c>
       <c r="R7" t="n">
-        <v>6463736</v>
+        <v>6463729</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1278,7 +1274,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Nyligen använt bo för häckning.</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127354741</v>
+        <v>127355148</v>
       </c>
       <c r="B8" t="n">
-        <v>57658</v>
+        <v>57674</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1316,16 +1312,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1343,7 +1339,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560773</v>
+        <v>560778</v>
       </c>
       <c r="R8" t="n">
-        <v>6463729</v>
+        <v>6463736</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Nyligen använt bo för häckning.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1641,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127360624</v>
+        <v>127355188</v>
       </c>
       <c r="B11" t="n">
-        <v>57658</v>
+        <v>57821</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1682,7 +1682,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560704</v>
+        <v>560790</v>
       </c>
       <c r="R11" t="n">
-        <v>6463675</v>
+        <v>6463749</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Försök till bobygge</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127355188</v>
+        <v>127360624</v>
       </c>
       <c r="B13" t="n">
-        <v>57821</v>
+        <v>57658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1918,7 +1918,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560790</v>
+        <v>560704</v>
       </c>
       <c r="R13" t="n">
-        <v>6463749</v>
+        <v>6463675</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Försök till bobygge</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2433,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127359702</v>
+        <v>127355403</v>
       </c>
       <c r="B18" t="n">
-        <v>79636</v>
+        <v>57658</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2444,26 +2444,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2471,10 +2484,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560825</v>
+        <v>560738</v>
       </c>
       <c r="R18" t="n">
-        <v>6463632</v>
+        <v>6463703</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2509,13 +2522,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2534,10 +2551,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127355403</v>
+        <v>127359702</v>
       </c>
       <c r="B19" t="n">
-        <v>57658</v>
+        <v>79636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,39 +2562,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2585,10 +2589,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560738</v>
+        <v>560825</v>
       </c>
       <c r="R19" t="n">
-        <v>6463703</v>
+        <v>6463632</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2623,17 +2627,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127354262</v>
+        <v>127355274</v>
       </c>
       <c r="B24" t="n">
-        <v>57658</v>
+        <v>91350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,39 +3090,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3130,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560850</v>
+        <v>560763</v>
       </c>
       <c r="R24" t="n">
-        <v>6463659</v>
+        <v>6463697</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3174,6 +3161,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3192,7 +3180,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127355274</v>
+        <v>127359680</v>
       </c>
       <c r="B25" t="n">
         <v>91350</v>
@@ -3230,10 +3218,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560763</v>
+        <v>560809</v>
       </c>
       <c r="R25" t="n">
-        <v>6463697</v>
+        <v>6463646</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3293,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127359680</v>
+        <v>127354262</v>
       </c>
       <c r="B26" t="n">
-        <v>91350</v>
+        <v>57658</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3304,26 +3292,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3331,10 +3332,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560809</v>
+        <v>560850</v>
       </c>
       <c r="R26" t="n">
-        <v>6463646</v>
+        <v>6463659</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3375,7 +3376,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127381942</v>
+        <v>127360157</v>
       </c>
       <c r="B31" t="n">
-        <v>79636</v>
+        <v>91350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,21 +3809,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560617</v>
+        <v>560850</v>
       </c>
       <c r="R31" t="n">
-        <v>6463688</v>
+        <v>6463569</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4139,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127360157</v>
+        <v>127381942</v>
       </c>
       <c r="B34" t="n">
-        <v>91350</v>
+        <v>79636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4150,21 +4150,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560850</v>
+        <v>560617</v>
       </c>
       <c r="R34" t="n">
-        <v>6463569</v>
+        <v>6463688</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4240,37 +4240,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127354652</v>
+        <v>127360190</v>
       </c>
       <c r="B35" t="n">
-        <v>91350</v>
+        <v>96050</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4278,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560773</v>
+        <v>560897</v>
       </c>
       <c r="R35" t="n">
-        <v>6463729</v>
+        <v>6463507</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4341,10 +4342,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127355375</v>
+        <v>127354652</v>
       </c>
       <c r="B36" t="n">
-        <v>79636</v>
+        <v>91350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4352,21 +4353,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4379,10 +4380,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560738</v>
+        <v>560773</v>
       </c>
       <c r="R36" t="n">
-        <v>6463703</v>
+        <v>6463729</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4442,38 +4443,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127360190</v>
+        <v>127355375</v>
       </c>
       <c r="B37" t="n">
-        <v>96050</v>
+        <v>79636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560897</v>
+        <v>560738</v>
       </c>
       <c r="R37" t="n">
-        <v>6463507</v>
+        <v>6463703</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4981,7 +4981,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127381965</v>
+        <v>127355339</v>
       </c>
       <c r="B42" t="n">
         <v>57658</v>
@@ -5019,7 +5019,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -5032,10 +5036,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>560624</v>
+        <v>560745</v>
       </c>
       <c r="R42" t="n">
-        <v>6463737</v>
+        <v>6463691</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5072,7 +5076,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5099,7 +5103,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127355339</v>
+        <v>127360701</v>
       </c>
       <c r="B43" t="n">
         <v>57658</v>
@@ -5137,14 +5141,10 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560745</v>
+        <v>560662</v>
       </c>
       <c r="R43" t="n">
-        <v>6463691</v>
+        <v>6463677</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5221,10 +5221,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127360121</v>
+        <v>127381965</v>
       </c>
       <c r="B44" t="n">
-        <v>57674</v>
+        <v>57658</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5232,16 +5232,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5272,10 +5272,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560850</v>
+        <v>560624</v>
       </c>
       <c r="R44" t="n">
-        <v>6463588</v>
+        <v>6463737</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Bohål, troligen mindre hackspett (ev större)</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5339,10 +5339,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127360701</v>
+        <v>127360121</v>
       </c>
       <c r="B45" t="n">
-        <v>57658</v>
+        <v>57674</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5350,16 +5350,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5380,7 +5380,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560662</v>
+        <v>560850</v>
       </c>
       <c r="R45" t="n">
-        <v>6463677</v>
+        <v>6463588</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Bohål, troligen mindre hackspett (ev större)</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127359699</v>
+        <v>127359702</v>
       </c>
       <c r="B17" t="n">
-        <v>91350</v>
+        <v>79636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,21 +2338,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2403,11 +2403,6 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Flera på samma träd</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2433,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127355403</v>
+        <v>127359699</v>
       </c>
       <c r="B18" t="n">
-        <v>57658</v>
+        <v>91350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2444,39 +2439,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2484,10 +2466,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560738</v>
+        <v>560825</v>
       </c>
       <c r="R18" t="n">
-        <v>6463703</v>
+        <v>6463632</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2524,7 +2506,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Flera på samma träd</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2533,6 +2515,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2551,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127359702</v>
+        <v>127355403</v>
       </c>
       <c r="B19" t="n">
-        <v>79636</v>
+        <v>57658</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,26 +2545,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2589,10 +2585,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560825</v>
+        <v>560738</v>
       </c>
       <c r="R19" t="n">
-        <v>6463632</v>
+        <v>6463703</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2627,13 +2623,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3495,10 +3495,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127359663</v>
+        <v>127360687</v>
       </c>
       <c r="B28" t="n">
-        <v>91350</v>
+        <v>79636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3506,21 +3506,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560780</v>
+        <v>560662</v>
       </c>
       <c r="R28" t="n">
-        <v>6463653</v>
+        <v>6463677</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3596,32 +3596,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127360687</v>
+        <v>127359655</v>
       </c>
       <c r="B29" t="n">
-        <v>79636</v>
+        <v>79104</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560662</v>
+        <v>560751</v>
       </c>
       <c r="R29" t="n">
-        <v>6463677</v>
+        <v>6463687</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127359655</v>
+        <v>127359663</v>
       </c>
       <c r="B30" t="n">
-        <v>79104</v>
+        <v>91350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6450</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560751</v>
+        <v>560780</v>
       </c>
       <c r="R30" t="n">
-        <v>6463687</v>
+        <v>6463653</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127355252</v>
       </c>
       <c r="B2" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,38 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127359952</v>
+        <v>127360839</v>
       </c>
       <c r="B3" t="n">
-        <v>97153</v>
+        <v>79638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2604</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560850</v>
+        <v>560571</v>
       </c>
       <c r="R3" t="n">
-        <v>6463588</v>
+        <v>6463719</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,37 +877,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127360839</v>
+        <v>127359952</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>97155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2604</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560571</v>
+        <v>560850</v>
       </c>
       <c r="R4" t="n">
-        <v>6463719</v>
+        <v>6463588</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,7 +982,7 @@
         <v>127355282</v>
       </c>
       <c r="B5" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127359945</v>
       </c>
       <c r="B6" t="n">
-        <v>97127</v>
+        <v>97129</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>127354741</v>
       </c>
       <c r="B7" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>127355148</v>
       </c>
       <c r="B8" t="n">
-        <v>57674</v>
+        <v>57676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>127355369</v>
       </c>
       <c r="B9" t="n">
-        <v>57655</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>127355314</v>
       </c>
       <c r="B10" t="n">
-        <v>91749</v>
+        <v>91751</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127355188</v>
+        <v>127360624</v>
       </c>
       <c r="B11" t="n">
-        <v>57821</v>
+        <v>57660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1682,7 +1682,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560790</v>
+        <v>560704</v>
       </c>
       <c r="R11" t="n">
-        <v>6463749</v>
+        <v>6463675</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Försök till bobygge</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1762,7 +1762,7 @@
         <v>127359896</v>
       </c>
       <c r="B12" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127360624</v>
+        <v>127355188</v>
       </c>
       <c r="B13" t="n">
-        <v>57658</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1918,7 +1918,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560704</v>
+        <v>560790</v>
       </c>
       <c r="R13" t="n">
-        <v>6463675</v>
+        <v>6463749</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Försök till bobygge</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1998,7 +1998,7 @@
         <v>127354529</v>
       </c>
       <c r="B14" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>127360820</v>
       </c>
       <c r="B15" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>127359646</v>
       </c>
       <c r="B16" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127359702</v>
+        <v>127355403</v>
       </c>
       <c r="B17" t="n">
-        <v>79636</v>
+        <v>57660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,26 +2338,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2365,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560825</v>
+        <v>560738</v>
       </c>
       <c r="R17" t="n">
-        <v>6463632</v>
+        <v>6463703</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2403,13 +2416,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2431,7 +2448,7 @@
         <v>127359699</v>
       </c>
       <c r="B18" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,10 +2551,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127355403</v>
+        <v>127359702</v>
       </c>
       <c r="B19" t="n">
-        <v>57658</v>
+        <v>79638</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,39 +2562,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2585,10 +2589,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560738</v>
+        <v>560825</v>
       </c>
       <c r="R19" t="n">
-        <v>6463703</v>
+        <v>6463632</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2623,17 +2627,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127382193</v>
+        <v>127359706</v>
       </c>
       <c r="B20" t="n">
-        <v>57658</v>
+        <v>5493</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,43 +2663,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>101410</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2707,10 +2692,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560809</v>
+        <v>560830</v>
       </c>
       <c r="R20" t="n">
-        <v>6463640</v>
+        <v>6463638</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2745,17 +2730,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Observerad</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2774,10 +2755,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127359706</v>
+        <v>127382193</v>
       </c>
       <c r="B21" t="n">
-        <v>5493</v>
+        <v>57660</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,28 +2766,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101410</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2814,10 +2810,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560830</v>
+        <v>560809</v>
       </c>
       <c r="R21" t="n">
-        <v>6463638</v>
+        <v>6463640</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2852,13 +2848,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Observerad</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>127360616</v>
       </c>
       <c r="B22" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>127359577</v>
       </c>
       <c r="B23" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127355274</v>
+        <v>127359680</v>
       </c>
       <c r="B24" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560763</v>
+        <v>560809</v>
       </c>
       <c r="R24" t="n">
-        <v>6463697</v>
+        <v>6463646</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127359680</v>
+        <v>127355274</v>
       </c>
       <c r="B25" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560809</v>
+        <v>560763</v>
       </c>
       <c r="R25" t="n">
-        <v>6463646</v>
+        <v>6463697</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3281,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127354262</v>
+        <v>127360466</v>
       </c>
       <c r="B26" t="n">
-        <v>57658</v>
+        <v>79638</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3292,39 +3292,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3332,10 +3319,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560850</v>
+        <v>560882</v>
       </c>
       <c r="R26" t="n">
-        <v>6463659</v>
+        <v>6463540</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3376,6 +3363,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3394,10 +3382,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127360466</v>
+        <v>127354262</v>
       </c>
       <c r="B27" t="n">
-        <v>79636</v>
+        <v>57660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3405,26 +3393,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3432,10 +3433,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560882</v>
+        <v>560850</v>
       </c>
       <c r="R27" t="n">
-        <v>6463540</v>
+        <v>6463659</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3476,7 +3477,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>127360687</v>
       </c>
       <c r="B28" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>127359655</v>
       </c>
       <c r="B29" t="n">
-        <v>79104</v>
+        <v>79106</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>127359663</v>
       </c>
       <c r="B30" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127360157</v>
+        <v>127381955</v>
       </c>
       <c r="B31" t="n">
-        <v>91350</v>
+        <v>57660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,26 +3809,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3836,10 +3849,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560850</v>
+        <v>560617</v>
       </c>
       <c r="R31" t="n">
-        <v>6463569</v>
+        <v>6463688</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3874,13 +3887,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3899,10 +3916,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127360220</v>
+        <v>127381942</v>
       </c>
       <c r="B32" t="n">
-        <v>57658</v>
+        <v>79638</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,43 +3927,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560903</v>
+        <v>560617</v>
       </c>
       <c r="R32" t="n">
-        <v>6463535</v>
+        <v>6463688</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3992,17 +3992,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Bebott bohål</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4021,10 +4017,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127381955</v>
+        <v>127360220</v>
       </c>
       <c r="B33" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4059,7 +4055,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560617</v>
+        <v>560903</v>
       </c>
       <c r="R33" t="n">
-        <v>6463688</v>
+        <v>6463535</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Bebott bohål</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4139,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127381942</v>
+        <v>127360157</v>
       </c>
       <c r="B34" t="n">
-        <v>79636</v>
+        <v>91352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4150,21 +4150,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560617</v>
+        <v>560850</v>
       </c>
       <c r="R34" t="n">
-        <v>6463688</v>
+        <v>6463569</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4243,7 +4243,7 @@
         <v>127360190</v>
       </c>
       <c r="B35" t="n">
-        <v>96050</v>
+        <v>96052</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>127354652</v>
       </c>
       <c r="B36" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>127355375</v>
       </c>
       <c r="B37" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4544,10 +4544,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127359873</v>
+        <v>127354580</v>
       </c>
       <c r="B38" t="n">
-        <v>91350</v>
+        <v>57660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,26 +4555,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4582,10 +4595,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560879</v>
+        <v>560782</v>
       </c>
       <c r="R38" t="n">
-        <v>6463611</v>
+        <v>6463706</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4620,13 +4633,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4645,10 +4662,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127354580</v>
+        <v>127359873</v>
       </c>
       <c r="B39" t="n">
-        <v>57658</v>
+        <v>91352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4656,39 +4673,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4696,10 +4700,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560782</v>
+        <v>560879</v>
       </c>
       <c r="R39" t="n">
-        <v>6463706</v>
+        <v>6463611</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4734,17 +4738,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4766,7 +4766,7 @@
         <v>127360176</v>
       </c>
       <c r="B40" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4880,10 +4880,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127360842</v>
+        <v>127355339</v>
       </c>
       <c r="B41" t="n">
-        <v>91350</v>
+        <v>57660</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4891,26 +4891,43 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4918,10 +4935,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>560551</v>
+        <v>560745</v>
       </c>
       <c r="R41" t="n">
-        <v>6463735</v>
+        <v>6463691</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4956,13 +4973,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4981,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127355339</v>
+        <v>127381965</v>
       </c>
       <c r="B42" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5019,11 +5040,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -5036,10 +5053,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>560745</v>
+        <v>560624</v>
       </c>
       <c r="R42" t="n">
-        <v>6463691</v>
+        <v>6463737</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5076,7 +5093,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5103,10 +5120,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127360701</v>
+        <v>127360121</v>
       </c>
       <c r="B43" t="n">
-        <v>57658</v>
+        <v>57676</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5114,16 +5131,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5144,7 +5161,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5154,10 +5171,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560662</v>
+        <v>560850</v>
       </c>
       <c r="R43" t="n">
-        <v>6463677</v>
+        <v>6463588</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5194,7 +5211,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Bohål, troligen mindre hackspett (ev större)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5221,10 +5238,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127381965</v>
+        <v>127360842</v>
       </c>
       <c r="B44" t="n">
-        <v>57658</v>
+        <v>91352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5232,39 +5249,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5272,10 +5276,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560624</v>
+        <v>560551</v>
       </c>
       <c r="R44" t="n">
-        <v>6463737</v>
+        <v>6463735</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5310,17 +5314,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5339,10 +5339,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127360121</v>
+        <v>127360701</v>
       </c>
       <c r="B45" t="n">
-        <v>57674</v>
+        <v>57660</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5350,16 +5350,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5380,7 +5380,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560850</v>
+        <v>560662</v>
       </c>
       <c r="R45" t="n">
-        <v>6463588</v>
+        <v>6463677</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Bohål, troligen mindre hackspett (ev större)</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -776,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127360839</v>
+        <v>127359952</v>
       </c>
       <c r="B3" t="n">
-        <v>79638</v>
+        <v>97155</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>2604</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -814,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560571</v>
+        <v>560850</v>
       </c>
       <c r="R3" t="n">
-        <v>6463719</v>
+        <v>6463588</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,38 +878,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127359952</v>
+        <v>127360839</v>
       </c>
       <c r="B4" t="n">
-        <v>97155</v>
+        <v>79638</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2604</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560850</v>
+        <v>560571</v>
       </c>
       <c r="R4" t="n">
-        <v>6463588</v>
+        <v>6463719</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127355369</v>
+        <v>127355314</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>91751</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,43 +1434,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102977</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1478,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560738</v>
+        <v>560745</v>
       </c>
       <c r="R9" t="n">
-        <v>6463703</v>
+        <v>6463691</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,6 +1505,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1540,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127355314</v>
+        <v>127355369</v>
       </c>
       <c r="B10" t="n">
-        <v>91751</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,26 +1535,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5420</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1578,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560745</v>
+        <v>560738</v>
       </c>
       <c r="R10" t="n">
-        <v>6463691</v>
+        <v>6463703</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1622,7 +1623,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1641,7 +1641,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127360624</v>
+        <v>127359896</v>
       </c>
       <c r="B11" t="n">
         <v>57660</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560704</v>
+        <v>560854</v>
       </c>
       <c r="R11" t="n">
-        <v>6463675</v>
+        <v>6463597</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,7 +1759,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127359896</v>
+        <v>127360624</v>
       </c>
       <c r="B12" t="n">
         <v>57660</v>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560854</v>
+        <v>560704</v>
       </c>
       <c r="R12" t="n">
-        <v>6463597</v>
+        <v>6463675</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127355403</v>
+        <v>127359699</v>
       </c>
       <c r="B17" t="n">
-        <v>57660</v>
+        <v>91352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,39 +2338,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2378,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560738</v>
+        <v>560825</v>
       </c>
       <c r="R17" t="n">
-        <v>6463703</v>
+        <v>6463632</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2418,7 +2405,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Flera på samma träd</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2427,6 +2414,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2445,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127359699</v>
+        <v>127355403</v>
       </c>
       <c r="B18" t="n">
-        <v>91352</v>
+        <v>57660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,26 +2444,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2483,10 +2484,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560825</v>
+        <v>560738</v>
       </c>
       <c r="R18" t="n">
-        <v>6463632</v>
+        <v>6463703</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2523,7 +2524,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Flera på samma träd</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2532,7 +2533,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127359706</v>
+        <v>127382193</v>
       </c>
       <c r="B20" t="n">
-        <v>5493</v>
+        <v>57660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,28 +2663,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101410</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2692,10 +2707,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560830</v>
+        <v>560809</v>
       </c>
       <c r="R20" t="n">
-        <v>6463638</v>
+        <v>6463640</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2730,13 +2745,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Observerad</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2755,10 +2774,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127382193</v>
+        <v>127360616</v>
       </c>
       <c r="B21" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2766,43 +2785,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2810,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560809</v>
+        <v>560704</v>
       </c>
       <c r="R21" t="n">
-        <v>6463640</v>
+        <v>6463675</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2848,17 +2850,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Observerad</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2877,10 +2875,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127360616</v>
+        <v>127359706</v>
       </c>
       <c r="B22" t="n">
-        <v>79638</v>
+        <v>5493</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2888,26 +2886,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560704</v>
+        <v>560830</v>
       </c>
       <c r="R22" t="n">
-        <v>6463675</v>
+        <v>6463638</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3281,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127360466</v>
+        <v>127354262</v>
       </c>
       <c r="B26" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3292,26 +3292,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3319,10 +3332,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560882</v>
+        <v>560850</v>
       </c>
       <c r="R26" t="n">
-        <v>6463540</v>
+        <v>6463659</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3363,7 +3376,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3382,10 +3394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127354262</v>
+        <v>127360466</v>
       </c>
       <c r="B27" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3393,39 +3405,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3433,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560850</v>
+        <v>560882</v>
       </c>
       <c r="R27" t="n">
-        <v>6463659</v>
+        <v>6463540</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3477,6 +3476,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3495,10 +3495,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127360687</v>
+        <v>127359663</v>
       </c>
       <c r="B28" t="n">
-        <v>79638</v>
+        <v>91352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3506,21 +3506,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560662</v>
+        <v>560780</v>
       </c>
       <c r="R28" t="n">
-        <v>6463677</v>
+        <v>6463653</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127359663</v>
+        <v>127360687</v>
       </c>
       <c r="B30" t="n">
-        <v>91352</v>
+        <v>79638</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560780</v>
+        <v>560662</v>
       </c>
       <c r="R30" t="n">
-        <v>6463653</v>
+        <v>6463677</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127381955</v>
+        <v>127360157</v>
       </c>
       <c r="B31" t="n">
-        <v>57660</v>
+        <v>91352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,39 +3809,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3849,10 +3836,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560617</v>
+        <v>560850</v>
       </c>
       <c r="R31" t="n">
-        <v>6463688</v>
+        <v>6463569</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3887,17 +3874,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4139,10 +4122,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127360157</v>
+        <v>127381955</v>
       </c>
       <c r="B34" t="n">
-        <v>91352</v>
+        <v>57660</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4150,26 +4133,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4177,10 +4173,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560850</v>
+        <v>560617</v>
       </c>
       <c r="R34" t="n">
-        <v>6463569</v>
+        <v>6463688</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4215,13 +4211,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4240,38 +4240,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127360190</v>
+        <v>127354652</v>
       </c>
       <c r="B35" t="n">
-        <v>96052</v>
+        <v>91352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4279,10 +4278,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560897</v>
+        <v>560773</v>
       </c>
       <c r="R35" t="n">
-        <v>6463507</v>
+        <v>6463729</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4342,10 +4341,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127354652</v>
+        <v>127355375</v>
       </c>
       <c r="B36" t="n">
-        <v>91352</v>
+        <v>79638</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4353,21 +4352,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4380,10 +4379,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560773</v>
+        <v>560738</v>
       </c>
       <c r="R36" t="n">
-        <v>6463729</v>
+        <v>6463703</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4443,37 +4442,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127355375</v>
+        <v>127360190</v>
       </c>
       <c r="B37" t="n">
-        <v>79638</v>
+        <v>96052</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560738</v>
+        <v>560897</v>
       </c>
       <c r="R37" t="n">
-        <v>6463703</v>
+        <v>6463507</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4544,10 +4544,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127354580</v>
+        <v>127359873</v>
       </c>
       <c r="B38" t="n">
-        <v>57660</v>
+        <v>91352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,39 +4555,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4595,10 +4582,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560782</v>
+        <v>560879</v>
       </c>
       <c r="R38" t="n">
-        <v>6463706</v>
+        <v>6463611</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4633,17 +4620,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4662,10 +4645,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127359873</v>
+        <v>127354580</v>
       </c>
       <c r="B39" t="n">
-        <v>91352</v>
+        <v>57660</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4673,26 +4656,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4700,10 +4696,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560879</v>
+        <v>560782</v>
       </c>
       <c r="R39" t="n">
-        <v>6463611</v>
+        <v>6463706</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4738,13 +4734,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4880,10 +4880,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127355339</v>
+        <v>127360842</v>
       </c>
       <c r="B41" t="n">
-        <v>57660</v>
+        <v>91352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4891,43 +4891,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4935,10 +4918,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>560745</v>
+        <v>560551</v>
       </c>
       <c r="R41" t="n">
-        <v>6463691</v>
+        <v>6463735</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4973,17 +4956,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5002,7 +4981,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127381965</v>
+        <v>127355339</v>
       </c>
       <c r="B42" t="n">
         <v>57660</v>
@@ -5040,7 +5019,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -5053,10 +5036,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>560624</v>
+        <v>560745</v>
       </c>
       <c r="R42" t="n">
-        <v>6463737</v>
+        <v>6463691</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5093,7 +5076,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5120,10 +5103,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127360121</v>
+        <v>127360701</v>
       </c>
       <c r="B43" t="n">
-        <v>57676</v>
+        <v>57660</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5131,16 +5114,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5161,7 +5144,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5171,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560850</v>
+        <v>560662</v>
       </c>
       <c r="R43" t="n">
-        <v>6463588</v>
+        <v>6463677</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5211,7 +5194,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Bohål, troligen mindre hackspett (ev större)</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5238,10 +5221,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127360842</v>
+        <v>127381965</v>
       </c>
       <c r="B44" t="n">
-        <v>91352</v>
+        <v>57660</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5249,26 +5232,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5276,10 +5272,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560551</v>
+        <v>560624</v>
       </c>
       <c r="R44" t="n">
-        <v>6463735</v>
+        <v>6463737</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5314,13 +5310,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5339,10 +5339,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127360701</v>
+        <v>127360121</v>
       </c>
       <c r="B45" t="n">
-        <v>57660</v>
+        <v>57676</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5350,16 +5350,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5380,7 +5380,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560662</v>
+        <v>560850</v>
       </c>
       <c r="R45" t="n">
-        <v>6463677</v>
+        <v>6463588</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Bohål, troligen mindre hackspett (ev större)</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -776,38 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127359952</v>
+        <v>127360839</v>
       </c>
       <c r="B3" t="n">
-        <v>97155</v>
+        <v>79638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2604</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560850</v>
+        <v>560571</v>
       </c>
       <c r="R3" t="n">
-        <v>6463588</v>
+        <v>6463719</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,37 +877,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127360839</v>
+        <v>127359952</v>
       </c>
       <c r="B4" t="n">
-        <v>79638</v>
+        <v>97155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2604</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560571</v>
+        <v>560850</v>
       </c>
       <c r="R4" t="n">
-        <v>6463719</v>
+        <v>6463588</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -3495,32 +3495,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127359663</v>
+        <v>127359655</v>
       </c>
       <c r="B28" t="n">
-        <v>91352</v>
+        <v>79106</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6450</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560780</v>
+        <v>560751</v>
       </c>
       <c r="R28" t="n">
-        <v>6463653</v>
+        <v>6463687</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3596,32 +3596,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127359655</v>
+        <v>127360687</v>
       </c>
       <c r="B29" t="n">
-        <v>79106</v>
+        <v>79638</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560751</v>
+        <v>560662</v>
       </c>
       <c r="R29" t="n">
-        <v>6463687</v>
+        <v>6463677</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127360687</v>
+        <v>127359663</v>
       </c>
       <c r="B30" t="n">
-        <v>79638</v>
+        <v>91352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560662</v>
+        <v>560780</v>
       </c>
       <c r="R30" t="n">
-        <v>6463677</v>
+        <v>6463653</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127360157</v>
+        <v>127360220</v>
       </c>
       <c r="B31" t="n">
-        <v>91352</v>
+        <v>57660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,26 +3809,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3836,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560850</v>
+        <v>560903</v>
       </c>
       <c r="R31" t="n">
-        <v>6463569</v>
+        <v>6463535</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3874,13 +3891,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Bebott bohål</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3899,10 +3920,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127381942</v>
+        <v>127381955</v>
       </c>
       <c r="B32" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,26 +3931,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3975,13 +4009,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4000,10 +4038,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127360220</v>
+        <v>127381942</v>
       </c>
       <c r="B33" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4011,43 +4049,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4055,10 +4076,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560903</v>
+        <v>560617</v>
       </c>
       <c r="R33" t="n">
-        <v>6463535</v>
+        <v>6463688</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4093,17 +4114,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Bebott bohål</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4122,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127381955</v>
+        <v>127360157</v>
       </c>
       <c r="B34" t="n">
-        <v>57660</v>
+        <v>91352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4133,39 +4150,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4173,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560617</v>
+        <v>560850</v>
       </c>
       <c r="R34" t="n">
-        <v>6463688</v>
+        <v>6463569</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4211,17 +4215,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4240,37 +4240,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127354652</v>
+        <v>127360190</v>
       </c>
       <c r="B35" t="n">
-        <v>91352</v>
+        <v>96052</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4278,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560773</v>
+        <v>560897</v>
       </c>
       <c r="R35" t="n">
-        <v>6463729</v>
+        <v>6463507</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4341,10 +4342,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127355375</v>
+        <v>127354652</v>
       </c>
       <c r="B36" t="n">
-        <v>79638</v>
+        <v>91352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4352,21 +4353,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4379,10 +4380,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560738</v>
+        <v>560773</v>
       </c>
       <c r="R36" t="n">
-        <v>6463703</v>
+        <v>6463729</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4442,38 +4443,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127360190</v>
+        <v>127355375</v>
       </c>
       <c r="B37" t="n">
-        <v>96052</v>
+        <v>79638</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560897</v>
+        <v>560738</v>
       </c>
       <c r="R37" t="n">
-        <v>6463507</v>
+        <v>6463703</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127355314</v>
+        <v>127355369</v>
       </c>
       <c r="B9" t="n">
-        <v>91751</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,26 +1434,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>102977</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1461,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560745</v>
+        <v>560738</v>
       </c>
       <c r="R9" t="n">
-        <v>6463691</v>
+        <v>6463703</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,7 +1522,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1524,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127355369</v>
+        <v>127355314</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>91751</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1535,43 +1551,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102977</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1579,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560738</v>
+        <v>560745</v>
       </c>
       <c r="R10" t="n">
-        <v>6463703</v>
+        <v>6463691</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1623,6 +1622,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127359699</v>
+        <v>127355403</v>
       </c>
       <c r="B17" t="n">
-        <v>91352</v>
+        <v>57660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,26 +2338,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2365,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560825</v>
+        <v>560738</v>
       </c>
       <c r="R17" t="n">
-        <v>6463632</v>
+        <v>6463703</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2405,7 +2418,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Flera på samma träd</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,7 +2427,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2433,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127355403</v>
+        <v>127359702</v>
       </c>
       <c r="B18" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2444,39 +2456,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2484,10 +2483,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560738</v>
+        <v>560825</v>
       </c>
       <c r="R18" t="n">
-        <v>6463703</v>
+        <v>6463632</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2522,17 +2521,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2551,10 +2546,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127359702</v>
+        <v>127359699</v>
       </c>
       <c r="B19" t="n">
-        <v>79638</v>
+        <v>91352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,21 +2557,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2627,6 +2622,11 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Flera på samma träd</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127382193</v>
+        <v>127359706</v>
       </c>
       <c r="B20" t="n">
-        <v>57660</v>
+        <v>5493</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,43 +2663,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>101410</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2707,10 +2692,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560809</v>
+        <v>560830</v>
       </c>
       <c r="R20" t="n">
-        <v>6463640</v>
+        <v>6463638</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2745,17 +2730,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Observerad</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2875,10 +2856,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127359706</v>
+        <v>127382193</v>
       </c>
       <c r="B22" t="n">
-        <v>5493</v>
+        <v>57660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2886,28 +2867,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101410</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2915,10 +2911,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560830</v>
+        <v>560809</v>
       </c>
       <c r="R22" t="n">
-        <v>6463638</v>
+        <v>6463640</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2953,13 +2949,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Observerad</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3079,7 +3079,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127359680</v>
+        <v>127355274</v>
       </c>
       <c r="B24" t="n">
         <v>91352</v>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560809</v>
+        <v>560763</v>
       </c>
       <c r="R24" t="n">
-        <v>6463646</v>
+        <v>6463697</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127355274</v>
+        <v>127360466</v>
       </c>
       <c r="B25" t="n">
-        <v>91352</v>
+        <v>79638</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,21 +3191,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560763</v>
+        <v>560882</v>
       </c>
       <c r="R25" t="n">
-        <v>6463697</v>
+        <v>6463540</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3281,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127354262</v>
+        <v>127359680</v>
       </c>
       <c r="B26" t="n">
-        <v>57660</v>
+        <v>91352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3292,39 +3292,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3332,10 +3319,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560850</v>
+        <v>560809</v>
       </c>
       <c r="R26" t="n">
-        <v>6463659</v>
+        <v>6463646</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3376,6 +3363,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3394,10 +3382,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127360466</v>
+        <v>127354262</v>
       </c>
       <c r="B27" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3405,26 +3393,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3432,10 +3433,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560882</v>
+        <v>560850</v>
       </c>
       <c r="R27" t="n">
-        <v>6463540</v>
+        <v>6463659</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3476,7 +3477,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3495,32 +3495,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127359655</v>
+        <v>127360687</v>
       </c>
       <c r="B28" t="n">
-        <v>79106</v>
+        <v>79638</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560751</v>
+        <v>560662</v>
       </c>
       <c r="R28" t="n">
-        <v>6463687</v>
+        <v>6463677</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3596,32 +3596,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127360687</v>
+        <v>127359655</v>
       </c>
       <c r="B29" t="n">
-        <v>79638</v>
+        <v>79106</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560662</v>
+        <v>560751</v>
       </c>
       <c r="R29" t="n">
-        <v>6463677</v>
+        <v>6463687</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127360220</v>
+        <v>127360157</v>
       </c>
       <c r="B31" t="n">
-        <v>57660</v>
+        <v>91352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,43 +3809,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3853,10 +3836,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560903</v>
+        <v>560850</v>
       </c>
       <c r="R31" t="n">
-        <v>6463535</v>
+        <v>6463569</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3891,17 +3874,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Bebott bohål</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3920,7 +3899,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127381955</v>
+        <v>127360220</v>
       </c>
       <c r="B32" t="n">
         <v>57660</v>
@@ -3958,7 +3937,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -3971,10 +3954,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560617</v>
+        <v>560903</v>
       </c>
       <c r="R32" t="n">
-        <v>6463688</v>
+        <v>6463535</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4011,7 +3994,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Bebott bohål</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4038,10 +4021,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127381942</v>
+        <v>127381955</v>
       </c>
       <c r="B33" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4049,26 +4032,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4114,13 +4110,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4139,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127360157</v>
+        <v>127381942</v>
       </c>
       <c r="B34" t="n">
-        <v>91352</v>
+        <v>79638</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4150,21 +4150,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560850</v>
+        <v>560617</v>
       </c>
       <c r="R34" t="n">
-        <v>6463569</v>
+        <v>6463688</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4240,38 +4240,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127360190</v>
+        <v>127354652</v>
       </c>
       <c r="B35" t="n">
-        <v>96052</v>
+        <v>91352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4279,10 +4278,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560897</v>
+        <v>560773</v>
       </c>
       <c r="R35" t="n">
-        <v>6463507</v>
+        <v>6463729</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4342,37 +4341,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127354652</v>
+        <v>127360190</v>
       </c>
       <c r="B36" t="n">
-        <v>91352</v>
+        <v>96052</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560773</v>
+        <v>560897</v>
       </c>
       <c r="R36" t="n">
-        <v>6463729</v>
+        <v>6463507</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4544,10 +4544,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127359873</v>
+        <v>127354580</v>
       </c>
       <c r="B38" t="n">
-        <v>91352</v>
+        <v>57660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,26 +4555,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4582,10 +4595,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560879</v>
+        <v>560782</v>
       </c>
       <c r="R38" t="n">
-        <v>6463611</v>
+        <v>6463706</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4620,13 +4633,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4645,10 +4662,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127354580</v>
+        <v>127359873</v>
       </c>
       <c r="B39" t="n">
-        <v>57660</v>
+        <v>91352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4656,39 +4673,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4696,10 +4700,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560782</v>
+        <v>560879</v>
       </c>
       <c r="R39" t="n">
-        <v>6463706</v>
+        <v>6463611</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4734,17 +4738,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127355252</v>
       </c>
       <c r="B2" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127360839</v>
+        <v>127359952</v>
       </c>
       <c r="B3" t="n">
-        <v>79638</v>
+        <v>97161</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>2604</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -814,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560571</v>
+        <v>560850</v>
       </c>
       <c r="R3" t="n">
-        <v>6463719</v>
+        <v>6463588</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,38 +878,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127359952</v>
+        <v>127360839</v>
       </c>
       <c r="B4" t="n">
-        <v>97155</v>
+        <v>79638</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2604</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560850</v>
+        <v>560571</v>
       </c>
       <c r="R4" t="n">
-        <v>6463588</v>
+        <v>6463719</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,7 +982,7 @@
         <v>127355282</v>
       </c>
       <c r="B5" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127359945</v>
       </c>
       <c r="B6" t="n">
-        <v>97129</v>
+        <v>97135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127354741</v>
+        <v>127355148</v>
       </c>
       <c r="B7" t="n">
-        <v>57660</v>
+        <v>57676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1221,7 +1221,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -1234,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560773</v>
+        <v>560778</v>
       </c>
       <c r="R7" t="n">
-        <v>6463729</v>
+        <v>6463736</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1274,7 +1278,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Nyligen använt bo för häckning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127355148</v>
+        <v>127354741</v>
       </c>
       <c r="B8" t="n">
-        <v>57676</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,16 +1316,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1339,11 +1343,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560778</v>
+        <v>560773</v>
       </c>
       <c r="R8" t="n">
-        <v>6463736</v>
+        <v>6463729</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Nyligen använt bo för häckning.</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127355369</v>
+        <v>127355314</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>91757</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,43 +1434,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102977</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1478,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560738</v>
+        <v>560745</v>
       </c>
       <c r="R9" t="n">
-        <v>6463703</v>
+        <v>6463691</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,6 +1505,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1540,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127355314</v>
+        <v>127355369</v>
       </c>
       <c r="B10" t="n">
-        <v>91751</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,26 +1535,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5420</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1578,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560745</v>
+        <v>560738</v>
       </c>
       <c r="R10" t="n">
-        <v>6463691</v>
+        <v>6463703</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1622,7 +1623,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1641,7 +1641,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127359896</v>
+        <v>127360624</v>
       </c>
       <c r="B11" t="n">
         <v>57660</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560854</v>
+        <v>560704</v>
       </c>
       <c r="R11" t="n">
-        <v>6463597</v>
+        <v>6463675</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,7 +1759,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127360624</v>
+        <v>127359896</v>
       </c>
       <c r="B12" t="n">
         <v>57660</v>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560704</v>
+        <v>560854</v>
       </c>
       <c r="R12" t="n">
-        <v>6463675</v>
+        <v>6463597</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1995,10 +1995,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127354529</v>
+        <v>127360820</v>
       </c>
       <c r="B14" t="n">
-        <v>91332</v>
+        <v>57660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,26 +2006,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2033,10 +2046,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560782</v>
+        <v>560582</v>
       </c>
       <c r="R14" t="n">
-        <v>6463706</v>
+        <v>6463723</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2077,7 +2090,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2096,7 +2108,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127360820</v>
+        <v>127359646</v>
       </c>
       <c r="B15" t="n">
         <v>57660</v>
@@ -2137,7 +2149,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2147,10 +2159,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560582</v>
+        <v>560751</v>
       </c>
       <c r="R15" t="n">
-        <v>6463723</v>
+        <v>6463687</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2183,6 +2195,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,10 +2226,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127359646</v>
+        <v>127354529</v>
       </c>
       <c r="B16" t="n">
-        <v>57660</v>
+        <v>91338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2220,39 +2237,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2260,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560751</v>
+        <v>560782</v>
       </c>
       <c r="R16" t="n">
-        <v>6463687</v>
+        <v>6463706</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2298,17 +2302,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127355403</v>
+        <v>127359702</v>
       </c>
       <c r="B17" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,39 +2338,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2378,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560738</v>
+        <v>560825</v>
       </c>
       <c r="R17" t="n">
-        <v>6463703</v>
+        <v>6463632</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2416,17 +2403,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2445,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127359702</v>
+        <v>127359699</v>
       </c>
       <c r="B18" t="n">
-        <v>79638</v>
+        <v>91358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2456,21 +2439,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2521,6 +2504,11 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Flera på samma träd</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2546,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127359699</v>
+        <v>127355403</v>
       </c>
       <c r="B19" t="n">
-        <v>91352</v>
+        <v>57660</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2557,26 +2545,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2584,10 +2585,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560825</v>
+        <v>560738</v>
       </c>
       <c r="R19" t="n">
-        <v>6463632</v>
+        <v>6463703</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2624,7 +2625,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Flera på samma träd</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2633,7 +2634,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2755,10 +2755,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127360616</v>
+        <v>127382193</v>
       </c>
       <c r="B21" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2766,26 +2766,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2793,10 +2810,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560704</v>
+        <v>560809</v>
       </c>
       <c r="R21" t="n">
-        <v>6463675</v>
+        <v>6463640</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2831,13 +2848,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Observerad</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2856,10 +2877,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127382193</v>
+        <v>127360616</v>
       </c>
       <c r="B22" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2867,43 +2888,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2911,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560809</v>
+        <v>560704</v>
       </c>
       <c r="R22" t="n">
-        <v>6463640</v>
+        <v>6463675</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2949,17 +2953,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Observerad</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>127359577</v>
       </c>
       <c r="B23" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127355274</v>
+        <v>127354262</v>
       </c>
       <c r="B24" t="n">
-        <v>91352</v>
+        <v>57660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,26 +3090,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3117,10 +3130,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560763</v>
+        <v>560850</v>
       </c>
       <c r="R24" t="n">
-        <v>6463697</v>
+        <v>6463659</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3161,7 +3174,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3284,7 +3296,7 @@
         <v>127359680</v>
       </c>
       <c r="B26" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3382,10 +3394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127354262</v>
+        <v>127355274</v>
       </c>
       <c r="B27" t="n">
-        <v>57660</v>
+        <v>91358</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3393,39 +3405,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3433,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560850</v>
+        <v>560763</v>
       </c>
       <c r="R27" t="n">
-        <v>6463659</v>
+        <v>6463697</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3477,6 +3476,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3495,10 +3495,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127360687</v>
+        <v>127359663</v>
       </c>
       <c r="B28" t="n">
-        <v>79638</v>
+        <v>91358</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3506,21 +3506,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560662</v>
+        <v>560780</v>
       </c>
       <c r="R28" t="n">
-        <v>6463677</v>
+        <v>6463653</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3596,32 +3596,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127359655</v>
+        <v>127360687</v>
       </c>
       <c r="B29" t="n">
-        <v>79106</v>
+        <v>79638</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560751</v>
+        <v>560662</v>
       </c>
       <c r="R29" t="n">
-        <v>6463687</v>
+        <v>6463677</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127359663</v>
+        <v>127359655</v>
       </c>
       <c r="B30" t="n">
-        <v>91352</v>
+        <v>79106</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6450</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560780</v>
+        <v>560751</v>
       </c>
       <c r="R30" t="n">
-        <v>6463653</v>
+        <v>6463687</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3801,7 +3801,7 @@
         <v>127360157</v>
       </c>
       <c r="B31" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127360220</v>
+        <v>127381942</v>
       </c>
       <c r="B32" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,43 +3910,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3954,10 +3937,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560903</v>
+        <v>560617</v>
       </c>
       <c r="R32" t="n">
-        <v>6463535</v>
+        <v>6463688</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3992,17 +3975,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Bebott bohål</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4021,7 +4000,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127381955</v>
+        <v>127360220</v>
       </c>
       <c r="B33" t="n">
         <v>57660</v>
@@ -4059,7 +4038,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4072,10 +4055,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560617</v>
+        <v>560903</v>
       </c>
       <c r="R33" t="n">
-        <v>6463688</v>
+        <v>6463535</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4112,7 +4095,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Bebott bohål</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4139,10 +4122,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127381942</v>
+        <v>127381955</v>
       </c>
       <c r="B34" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4150,26 +4133,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4215,13 +4211,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>127354652</v>
       </c>
       <c r="B35" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>127360190</v>
       </c>
       <c r="B36" t="n">
-        <v>96052</v>
+        <v>96058</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>127359873</v>
       </c>
       <c r="B39" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>127360842</v>
       </c>
       <c r="B41" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127355339</v>
+        <v>127381965</v>
       </c>
       <c r="B42" t="n">
         <v>57660</v>
@@ -5019,11 +5019,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -5036,10 +5032,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>560745</v>
+        <v>560624</v>
       </c>
       <c r="R42" t="n">
-        <v>6463691</v>
+        <v>6463737</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5076,7 +5072,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5103,7 +5099,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127360701</v>
+        <v>127355339</v>
       </c>
       <c r="B43" t="n">
         <v>57660</v>
@@ -5141,10 +5137,14 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560662</v>
+        <v>560745</v>
       </c>
       <c r="R43" t="n">
-        <v>6463677</v>
+        <v>6463691</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5221,10 +5221,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127381965</v>
+        <v>127360121</v>
       </c>
       <c r="B44" t="n">
-        <v>57660</v>
+        <v>57676</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5232,16 +5232,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5272,10 +5272,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560624</v>
+        <v>560850</v>
       </c>
       <c r="R44" t="n">
-        <v>6463737</v>
+        <v>6463588</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Bohål, troligen mindre hackspett (ev större)</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5339,10 +5339,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127360121</v>
+        <v>127360701</v>
       </c>
       <c r="B45" t="n">
-        <v>57676</v>
+        <v>57660</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5350,16 +5350,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5380,7 +5380,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560850</v>
+        <v>560662</v>
       </c>
       <c r="R45" t="n">
-        <v>6463588</v>
+        <v>6463677</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Bohål, troligen mindre hackspett (ev större)</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127355252</v>
       </c>
       <c r="B2" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127359952</v>
       </c>
       <c r="B3" t="n">
-        <v>97161</v>
+        <v>97164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127360839</v>
       </c>
       <c r="B4" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>127355282</v>
       </c>
       <c r="B5" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127359945</v>
       </c>
       <c r="B6" t="n">
-        <v>97135</v>
+        <v>97138</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127355148</v>
+        <v>127354741</v>
       </c>
       <c r="B7" t="n">
-        <v>57676</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1221,11 +1221,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -1238,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560778</v>
+        <v>560773</v>
       </c>
       <c r="R7" t="n">
-        <v>6463736</v>
+        <v>6463729</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1278,7 +1274,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Nyligen använt bo för häckning.</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127354741</v>
+        <v>127355148</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>57679</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1316,16 +1312,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1343,7 +1339,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560773</v>
+        <v>560778</v>
       </c>
       <c r="R8" t="n">
-        <v>6463729</v>
+        <v>6463736</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Nyligen använt bo för häckning.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,7 +1426,7 @@
         <v>127355314</v>
       </c>
       <c r="B9" t="n">
-        <v>91757</v>
+        <v>91760</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>127355369</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127360624</v>
+        <v>127359896</v>
       </c>
       <c r="B11" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560704</v>
+        <v>560854</v>
       </c>
       <c r="R11" t="n">
-        <v>6463675</v>
+        <v>6463597</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127359896</v>
+        <v>127360624</v>
       </c>
       <c r="B12" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560854</v>
+        <v>560704</v>
       </c>
       <c r="R12" t="n">
-        <v>6463597</v>
+        <v>6463675</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,7 +1880,7 @@
         <v>127355188</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127360820</v>
+        <v>127354529</v>
       </c>
       <c r="B14" t="n">
-        <v>57660</v>
+        <v>91341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,39 +2006,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2046,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560582</v>
+        <v>560782</v>
       </c>
       <c r="R14" t="n">
-        <v>6463723</v>
+        <v>6463706</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2090,6 +2077,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2108,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127359646</v>
+        <v>127360820</v>
       </c>
       <c r="B15" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2149,7 +2137,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2159,10 +2147,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560751</v>
+        <v>560582</v>
       </c>
       <c r="R15" t="n">
-        <v>6463687</v>
+        <v>6463723</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2195,11 +2183,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2226,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127354529</v>
+        <v>127359646</v>
       </c>
       <c r="B16" t="n">
-        <v>91338</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,26 +2220,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2264,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560782</v>
+        <v>560751</v>
       </c>
       <c r="R16" t="n">
-        <v>6463706</v>
+        <v>6463687</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2302,13 +2298,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>127359702</v>
       </c>
       <c r="B17" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>127359699</v>
       </c>
       <c r="B18" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>127355403</v>
       </c>
       <c r="B19" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127359706</v>
+        <v>127360616</v>
       </c>
       <c r="B20" t="n">
-        <v>5493</v>
+        <v>79641</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,28 +2663,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2692,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560830</v>
+        <v>560704</v>
       </c>
       <c r="R20" t="n">
-        <v>6463638</v>
+        <v>6463675</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2758,7 +2756,7 @@
         <v>127382193</v>
       </c>
       <c r="B21" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2877,10 +2875,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127360616</v>
+        <v>127359706</v>
       </c>
       <c r="B22" t="n">
-        <v>79638</v>
+        <v>5493</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2888,26 +2886,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560704</v>
+        <v>560830</v>
       </c>
       <c r="R22" t="n">
-        <v>6463675</v>
+        <v>6463638</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2981,7 +2981,7 @@
         <v>127359577</v>
       </c>
       <c r="B23" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127354262</v>
+        <v>127360466</v>
       </c>
       <c r="B24" t="n">
-        <v>57660</v>
+        <v>79641</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,39 +3090,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3130,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560850</v>
+        <v>560882</v>
       </c>
       <c r="R24" t="n">
-        <v>6463659</v>
+        <v>6463540</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3174,6 +3161,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3192,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127360466</v>
+        <v>127359680</v>
       </c>
       <c r="B25" t="n">
-        <v>79638</v>
+        <v>91361</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3203,21 +3191,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3230,10 +3218,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560882</v>
+        <v>560809</v>
       </c>
       <c r="R25" t="n">
-        <v>6463540</v>
+        <v>6463646</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3293,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127359680</v>
+        <v>127355274</v>
       </c>
       <c r="B26" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3331,10 +3319,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560809</v>
+        <v>560763</v>
       </c>
       <c r="R26" t="n">
-        <v>6463646</v>
+        <v>6463697</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3394,10 +3382,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127355274</v>
+        <v>127354262</v>
       </c>
       <c r="B27" t="n">
-        <v>91358</v>
+        <v>57663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3405,26 +3393,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3432,10 +3433,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560763</v>
+        <v>560850</v>
       </c>
       <c r="R27" t="n">
-        <v>6463697</v>
+        <v>6463659</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3476,7 +3477,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3495,10 +3495,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127359663</v>
+        <v>127360687</v>
       </c>
       <c r="B28" t="n">
-        <v>91358</v>
+        <v>79641</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3506,21 +3506,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560780</v>
+        <v>560662</v>
       </c>
       <c r="R28" t="n">
-        <v>6463653</v>
+        <v>6463677</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3596,32 +3596,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127360687</v>
+        <v>127359655</v>
       </c>
       <c r="B29" t="n">
-        <v>79638</v>
+        <v>79109</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560662</v>
+        <v>560751</v>
       </c>
       <c r="R29" t="n">
-        <v>6463677</v>
+        <v>6463687</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127359655</v>
+        <v>127359663</v>
       </c>
       <c r="B30" t="n">
-        <v>79106</v>
+        <v>91361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6450</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560751</v>
+        <v>560780</v>
       </c>
       <c r="R30" t="n">
-        <v>6463687</v>
+        <v>6463653</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127360157</v>
+        <v>127360220</v>
       </c>
       <c r="B31" t="n">
-        <v>91358</v>
+        <v>57663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,26 +3809,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3836,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560850</v>
+        <v>560903</v>
       </c>
       <c r="R31" t="n">
-        <v>6463569</v>
+        <v>6463535</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3874,13 +3891,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Bebott bohål</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3902,7 +3923,7 @@
         <v>127381942</v>
       </c>
       <c r="B32" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,10 +4021,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127360220</v>
+        <v>127360157</v>
       </c>
       <c r="B33" t="n">
-        <v>57660</v>
+        <v>91361</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4011,43 +4032,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4055,10 +4059,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560903</v>
+        <v>560850</v>
       </c>
       <c r="R33" t="n">
-        <v>6463535</v>
+        <v>6463569</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4093,17 +4097,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Bebott bohål</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>127381955</v>
       </c>
       <c r="B34" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4240,37 +4240,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127354652</v>
+        <v>127360190</v>
       </c>
       <c r="B35" t="n">
-        <v>91358</v>
+        <v>96061</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4278,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560773</v>
+        <v>560897</v>
       </c>
       <c r="R35" t="n">
-        <v>6463729</v>
+        <v>6463507</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4341,38 +4342,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127360190</v>
+        <v>127354652</v>
       </c>
       <c r="B36" t="n">
-        <v>96058</v>
+        <v>91361</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560897</v>
+        <v>560773</v>
       </c>
       <c r="R36" t="n">
-        <v>6463507</v>
+        <v>6463729</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4446,7 +4446,7 @@
         <v>127355375</v>
       </c>
       <c r="B37" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4544,10 +4544,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127354580</v>
+        <v>127359873</v>
       </c>
       <c r="B38" t="n">
-        <v>57660</v>
+        <v>91361</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,39 +4555,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4595,10 +4582,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560782</v>
+        <v>560879</v>
       </c>
       <c r="R38" t="n">
-        <v>6463706</v>
+        <v>6463611</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4633,17 +4620,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4662,10 +4645,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127359873</v>
+        <v>127354580</v>
       </c>
       <c r="B39" t="n">
-        <v>91358</v>
+        <v>57663</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4673,26 +4656,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4700,10 +4696,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560879</v>
+        <v>560782</v>
       </c>
       <c r="R39" t="n">
-        <v>6463611</v>
+        <v>6463706</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4738,13 +4734,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4766,7 +4766,7 @@
         <v>127360176</v>
       </c>
       <c r="B40" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>127360842</v>
       </c>
       <c r="B41" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4981,10 +4981,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127381965</v>
+        <v>127355339</v>
       </c>
       <c r="B42" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5019,7 +5019,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -5032,10 +5036,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>560624</v>
+        <v>560745</v>
       </c>
       <c r="R42" t="n">
-        <v>6463737</v>
+        <v>6463691</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5072,7 +5076,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5099,10 +5103,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127355339</v>
+        <v>127360701</v>
       </c>
       <c r="B43" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,14 +5141,10 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560745</v>
+        <v>560662</v>
       </c>
       <c r="R43" t="n">
-        <v>6463691</v>
+        <v>6463677</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5221,10 +5221,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127360121</v>
+        <v>127381965</v>
       </c>
       <c r="B44" t="n">
-        <v>57676</v>
+        <v>57663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5232,16 +5232,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5272,10 +5272,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560850</v>
+        <v>560624</v>
       </c>
       <c r="R44" t="n">
-        <v>6463588</v>
+        <v>6463737</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Bohål, troligen mindre hackspett (ev större)</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5339,10 +5339,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127360701</v>
+        <v>127360121</v>
       </c>
       <c r="B45" t="n">
-        <v>57660</v>
+        <v>57679</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5350,16 +5350,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5380,7 +5380,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560662</v>
+        <v>560850</v>
       </c>
       <c r="R45" t="n">
-        <v>6463677</v>
+        <v>6463588</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Bohål, troligen mindre hackspett (ev större)</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127355252</v>
       </c>
       <c r="B2" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,38 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127359952</v>
+        <v>127360839</v>
       </c>
       <c r="B3" t="n">
-        <v>97164</v>
+        <v>79647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2604</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560850</v>
+        <v>560571</v>
       </c>
       <c r="R3" t="n">
-        <v>6463588</v>
+        <v>6463719</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,37 +877,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127360839</v>
+        <v>127359952</v>
       </c>
       <c r="B4" t="n">
-        <v>79641</v>
+        <v>97172</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2604</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560571</v>
+        <v>560850</v>
       </c>
       <c r="R4" t="n">
-        <v>6463719</v>
+        <v>6463588</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,7 +982,7 @@
         <v>127355282</v>
       </c>
       <c r="B5" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127359945</v>
       </c>
       <c r="B6" t="n">
-        <v>97138</v>
+        <v>97146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>127354741</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>127355148</v>
       </c>
       <c r="B8" t="n">
-        <v>57679</v>
+        <v>57685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127355314</v>
+        <v>127355369</v>
       </c>
       <c r="B9" t="n">
-        <v>91760</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,26 +1434,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>102977</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1461,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560745</v>
+        <v>560738</v>
       </c>
       <c r="R9" t="n">
-        <v>6463691</v>
+        <v>6463703</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,7 +1522,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1524,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127355369</v>
+        <v>127355314</v>
       </c>
       <c r="B10" t="n">
-        <v>57660</v>
+        <v>91768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1535,43 +1551,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102977</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1579,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560738</v>
+        <v>560745</v>
       </c>
       <c r="R10" t="n">
-        <v>6463703</v>
+        <v>6463691</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1623,6 +1622,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1644,7 +1644,7 @@
         <v>127359896</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127360624</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>127355188</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127354529</v>
+        <v>127360820</v>
       </c>
       <c r="B14" t="n">
-        <v>91341</v>
+        <v>57669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,26 +2006,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2033,10 +2046,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560782</v>
+        <v>560582</v>
       </c>
       <c r="R14" t="n">
-        <v>6463706</v>
+        <v>6463723</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2077,7 +2090,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2096,10 +2108,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127360820</v>
+        <v>127359646</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2137,7 +2149,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2147,10 +2159,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560582</v>
+        <v>560751</v>
       </c>
       <c r="R15" t="n">
-        <v>6463723</v>
+        <v>6463687</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2183,6 +2195,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,10 +2226,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127359646</v>
+        <v>127354529</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>91349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2220,39 +2237,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2260,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560751</v>
+        <v>560782</v>
       </c>
       <c r="R16" t="n">
-        <v>6463687</v>
+        <v>6463706</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2298,17 +2302,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127359702</v>
+        <v>127359699</v>
       </c>
       <c r="B17" t="n">
-        <v>79641</v>
+        <v>91369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,21 +2338,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2403,6 +2403,11 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Flera på samma träd</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2428,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127359699</v>
+        <v>127359702</v>
       </c>
       <c r="B18" t="n">
-        <v>91361</v>
+        <v>79647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2439,21 +2444,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2504,11 +2509,6 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Flera på samma träd</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>127355403</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127360616</v>
+        <v>127382193</v>
       </c>
       <c r="B20" t="n">
-        <v>79641</v>
+        <v>57669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,26 +2663,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2690,10 +2707,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560704</v>
+        <v>560809</v>
       </c>
       <c r="R20" t="n">
-        <v>6463675</v>
+        <v>6463640</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2728,13 +2745,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Observerad</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2753,10 +2774,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127382193</v>
+        <v>127360616</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>79647</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2764,43 +2785,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2808,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560809</v>
+        <v>560704</v>
       </c>
       <c r="R21" t="n">
-        <v>6463640</v>
+        <v>6463675</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2846,17 +2850,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Observerad</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>127359577</v>
       </c>
       <c r="B23" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127360466</v>
+        <v>127355274</v>
       </c>
       <c r="B24" t="n">
-        <v>79641</v>
+        <v>91369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,21 +3090,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560882</v>
+        <v>560763</v>
       </c>
       <c r="R24" t="n">
-        <v>6463540</v>
+        <v>6463697</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3183,7 +3183,7 @@
         <v>127359680</v>
       </c>
       <c r="B25" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127355274</v>
+        <v>127354262</v>
       </c>
       <c r="B26" t="n">
-        <v>91361</v>
+        <v>57669</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3292,26 +3292,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3319,10 +3332,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560763</v>
+        <v>560850</v>
       </c>
       <c r="R26" t="n">
-        <v>6463697</v>
+        <v>6463659</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3363,7 +3376,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3382,10 +3394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127354262</v>
+        <v>127360466</v>
       </c>
       <c r="B27" t="n">
-        <v>57663</v>
+        <v>79647</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3393,39 +3405,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3433,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560850</v>
+        <v>560882</v>
       </c>
       <c r="R27" t="n">
-        <v>6463659</v>
+        <v>6463540</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3477,6 +3476,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3495,10 +3495,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127360687</v>
+        <v>127359663</v>
       </c>
       <c r="B28" t="n">
-        <v>79641</v>
+        <v>91369</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3506,21 +3506,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560662</v>
+        <v>560780</v>
       </c>
       <c r="R28" t="n">
-        <v>6463677</v>
+        <v>6463653</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3596,32 +3596,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127359655</v>
+        <v>127360687</v>
       </c>
       <c r="B29" t="n">
-        <v>79109</v>
+        <v>79647</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560751</v>
+        <v>560662</v>
       </c>
       <c r="R29" t="n">
-        <v>6463687</v>
+        <v>6463677</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127359663</v>
+        <v>127359655</v>
       </c>
       <c r="B30" t="n">
-        <v>91361</v>
+        <v>79115</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6450</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560780</v>
+        <v>560751</v>
       </c>
       <c r="R30" t="n">
-        <v>6463653</v>
+        <v>6463687</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127360220</v>
+        <v>127360157</v>
       </c>
       <c r="B31" t="n">
-        <v>57663</v>
+        <v>91369</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,43 +3809,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3853,10 +3836,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560903</v>
+        <v>560850</v>
       </c>
       <c r="R31" t="n">
-        <v>6463535</v>
+        <v>6463569</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3891,17 +3874,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Bebott bohål</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3923,7 +3902,7 @@
         <v>127381942</v>
       </c>
       <c r="B32" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4021,10 +4000,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127360157</v>
+        <v>127360220</v>
       </c>
       <c r="B33" t="n">
-        <v>91361</v>
+        <v>57669</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4032,26 +4011,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4059,10 +4055,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560850</v>
+        <v>560903</v>
       </c>
       <c r="R33" t="n">
-        <v>6463569</v>
+        <v>6463535</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4097,13 +4093,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Bebott bohål</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>127381955</v>
       </c>
       <c r="B34" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4240,38 +4240,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127360190</v>
+        <v>127355375</v>
       </c>
       <c r="B35" t="n">
-        <v>96061</v>
+        <v>79647</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4279,10 +4278,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560897</v>
+        <v>560738</v>
       </c>
       <c r="R35" t="n">
-        <v>6463507</v>
+        <v>6463703</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4342,37 +4341,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127354652</v>
+        <v>127360190</v>
       </c>
       <c r="B36" t="n">
-        <v>91361</v>
+        <v>96069</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560773</v>
+        <v>560897</v>
       </c>
       <c r="R36" t="n">
-        <v>6463729</v>
+        <v>6463507</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4443,10 +4443,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127355375</v>
+        <v>127354652</v>
       </c>
       <c r="B37" t="n">
-        <v>79641</v>
+        <v>91369</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4454,21 +4454,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560738</v>
+        <v>560773</v>
       </c>
       <c r="R37" t="n">
-        <v>6463703</v>
+        <v>6463729</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4547,7 +4547,7 @@
         <v>127359873</v>
       </c>
       <c r="B38" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>127354580</v>
       </c>
       <c r="B39" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>127360176</v>
       </c>
       <c r="B40" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>127360842</v>
       </c>
       <c r="B41" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>127355339</v>
       </c>
       <c r="B42" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>127360701</v>
       </c>
       <c r="B43" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>127381965</v>
       </c>
       <c r="B44" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>127360121</v>
       </c>
       <c r="B45" t="n">
-        <v>57679</v>
+        <v>57685</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127355252</v>
       </c>
       <c r="B2" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127360839</v>
+        <v>127359952</v>
       </c>
       <c r="B3" t="n">
-        <v>79647</v>
+        <v>97173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>2604</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -814,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560571</v>
+        <v>560850</v>
       </c>
       <c r="R3" t="n">
-        <v>6463719</v>
+        <v>6463588</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,38 +878,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127359952</v>
+        <v>127360839</v>
       </c>
       <c r="B4" t="n">
-        <v>97172</v>
+        <v>79647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2604</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560850</v>
+        <v>560571</v>
       </c>
       <c r="R4" t="n">
-        <v>6463588</v>
+        <v>6463719</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,7 +982,7 @@
         <v>127355282</v>
       </c>
       <c r="B5" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127359945</v>
       </c>
       <c r="B6" t="n">
-        <v>97146</v>
+        <v>97147</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127355369</v>
+        <v>127355314</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>91769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,43 +1434,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102977</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1478,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560738</v>
+        <v>560745</v>
       </c>
       <c r="R9" t="n">
-        <v>6463703</v>
+        <v>6463691</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,6 +1505,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1540,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127355314</v>
+        <v>127355369</v>
       </c>
       <c r="B10" t="n">
-        <v>91768</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,26 +1535,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5420</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1578,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560745</v>
+        <v>560738</v>
       </c>
       <c r="R10" t="n">
-        <v>6463691</v>
+        <v>6463703</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1622,7 +1623,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127359896</v>
+        <v>127355188</v>
       </c>
       <c r="B11" t="n">
-        <v>57669</v>
+        <v>57832</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1682,7 +1682,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560854</v>
+        <v>560790</v>
       </c>
       <c r="R11" t="n">
-        <v>6463597</v>
+        <v>6463749</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Försök till bobygge</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,7 +1759,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127360624</v>
+        <v>127359896</v>
       </c>
       <c r="B12" t="n">
         <v>57669</v>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560704</v>
+        <v>560854</v>
       </c>
       <c r="R12" t="n">
-        <v>6463675</v>
+        <v>6463597</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127355188</v>
+        <v>127360624</v>
       </c>
       <c r="B13" t="n">
-        <v>57832</v>
+        <v>57669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1918,7 +1918,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560790</v>
+        <v>560704</v>
       </c>
       <c r="R13" t="n">
-        <v>6463749</v>
+        <v>6463675</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Försök till bobygge</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2229,7 +2229,7 @@
         <v>127354529</v>
       </c>
       <c r="B16" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127359699</v>
+        <v>127359702</v>
       </c>
       <c r="B17" t="n">
-        <v>91369</v>
+        <v>79647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,21 +2338,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2403,11 +2403,6 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Flera på samma träd</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2433,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127359702</v>
+        <v>127359699</v>
       </c>
       <c r="B18" t="n">
-        <v>79647</v>
+        <v>91370</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2444,21 +2439,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2509,6 +2504,11 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Flera på samma träd</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127382193</v>
+        <v>127360616</v>
       </c>
       <c r="B20" t="n">
-        <v>57669</v>
+        <v>79647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,43 +2663,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2707,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560809</v>
+        <v>560704</v>
       </c>
       <c r="R20" t="n">
-        <v>6463640</v>
+        <v>6463675</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2745,17 +2728,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Observerad</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2774,10 +2753,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127360616</v>
+        <v>127382193</v>
       </c>
       <c r="B21" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,26 +2764,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2812,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560704</v>
+        <v>560809</v>
       </c>
       <c r="R21" t="n">
-        <v>6463675</v>
+        <v>6463640</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2850,13 +2846,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Observerad</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>127359577</v>
       </c>
       <c r="B23" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127355274</v>
+        <v>127354262</v>
       </c>
       <c r="B24" t="n">
-        <v>91369</v>
+        <v>57669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,26 +3090,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3117,10 +3130,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560763</v>
+        <v>560850</v>
       </c>
       <c r="R24" t="n">
-        <v>6463697</v>
+        <v>6463659</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3161,7 +3174,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3180,10 +3192,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127359680</v>
+        <v>127360466</v>
       </c>
       <c r="B25" t="n">
-        <v>91369</v>
+        <v>79647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,21 +3203,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3218,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560809</v>
+        <v>560882</v>
       </c>
       <c r="R25" t="n">
-        <v>6463646</v>
+        <v>6463540</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3281,10 +3293,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127354262</v>
+        <v>127359680</v>
       </c>
       <c r="B26" t="n">
-        <v>57669</v>
+        <v>91370</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3292,39 +3304,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3332,10 +3331,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560850</v>
+        <v>560809</v>
       </c>
       <c r="R26" t="n">
-        <v>6463659</v>
+        <v>6463646</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3376,6 +3375,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3394,10 +3394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127360466</v>
+        <v>127355274</v>
       </c>
       <c r="B27" t="n">
-        <v>79647</v>
+        <v>91370</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3405,21 +3405,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560882</v>
+        <v>560763</v>
       </c>
       <c r="R27" t="n">
-        <v>6463540</v>
+        <v>6463697</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3495,32 +3495,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127359663</v>
+        <v>127359655</v>
       </c>
       <c r="B28" t="n">
-        <v>91369</v>
+        <v>79115</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6450</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560780</v>
+        <v>560751</v>
       </c>
       <c r="R28" t="n">
-        <v>6463653</v>
+        <v>6463687</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127360687</v>
+        <v>127359663</v>
       </c>
       <c r="B29" t="n">
-        <v>79647</v>
+        <v>91370</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560662</v>
+        <v>560780</v>
       </c>
       <c r="R29" t="n">
-        <v>6463677</v>
+        <v>6463653</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127359655</v>
+        <v>127360687</v>
       </c>
       <c r="B30" t="n">
-        <v>79115</v>
+        <v>79647</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560751</v>
+        <v>560662</v>
       </c>
       <c r="R30" t="n">
-        <v>6463687</v>
+        <v>6463677</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127360157</v>
+        <v>127381942</v>
       </c>
       <c r="B31" t="n">
-        <v>91369</v>
+        <v>79647</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,21 +3809,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560850</v>
+        <v>560617</v>
       </c>
       <c r="R31" t="n">
-        <v>6463569</v>
+        <v>6463688</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127381942</v>
+        <v>127360157</v>
       </c>
       <c r="B32" t="n">
-        <v>79647</v>
+        <v>91370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560617</v>
+        <v>560850</v>
       </c>
       <c r="R32" t="n">
-        <v>6463688</v>
+        <v>6463569</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4240,37 +4240,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127355375</v>
+        <v>127360190</v>
       </c>
       <c r="B35" t="n">
-        <v>79647</v>
+        <v>96070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4278,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560738</v>
+        <v>560897</v>
       </c>
       <c r="R35" t="n">
-        <v>6463703</v>
+        <v>6463507</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4341,38 +4342,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127360190</v>
+        <v>127355375</v>
       </c>
       <c r="B36" t="n">
-        <v>96069</v>
+        <v>79647</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560897</v>
+        <v>560738</v>
       </c>
       <c r="R36" t="n">
-        <v>6463507</v>
+        <v>6463703</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4446,7 +4446,7 @@
         <v>127354652</v>
       </c>
       <c r="B37" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>127359873</v>
       </c>
       <c r="B38" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>127360842</v>
       </c>
       <c r="B41" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127355314</v>
+        <v>127355369</v>
       </c>
       <c r="B9" t="n">
-        <v>91769</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,26 +1434,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>102977</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1461,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560745</v>
+        <v>560738</v>
       </c>
       <c r="R9" t="n">
-        <v>6463691</v>
+        <v>6463703</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,7 +1522,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1524,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127355369</v>
+        <v>127355314</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>91769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1535,43 +1551,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102977</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1579,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560738</v>
+        <v>560745</v>
       </c>
       <c r="R10" t="n">
-        <v>6463703</v>
+        <v>6463691</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1623,6 +1622,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127355188</v>
+        <v>127359896</v>
       </c>
       <c r="B11" t="n">
-        <v>57832</v>
+        <v>57669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1682,7 +1682,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560790</v>
+        <v>560854</v>
       </c>
       <c r="R11" t="n">
-        <v>6463749</v>
+        <v>6463597</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Försök till bobygge</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,7 +1759,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127359896</v>
+        <v>127360624</v>
       </c>
       <c r="B12" t="n">
         <v>57669</v>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560854</v>
+        <v>560704</v>
       </c>
       <c r="R12" t="n">
-        <v>6463597</v>
+        <v>6463675</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127360624</v>
+        <v>127355188</v>
       </c>
       <c r="B13" t="n">
-        <v>57669</v>
+        <v>57832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1918,7 +1918,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560704</v>
+        <v>560790</v>
       </c>
       <c r="R13" t="n">
-        <v>6463675</v>
+        <v>6463749</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Försök till bobygge</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1995,10 +1995,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127360820</v>
+        <v>127354529</v>
       </c>
       <c r="B14" t="n">
-        <v>57669</v>
+        <v>91350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,39 +2006,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2046,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560582</v>
+        <v>560782</v>
       </c>
       <c r="R14" t="n">
-        <v>6463723</v>
+        <v>6463706</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2090,6 +2077,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2108,7 +2096,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127359646</v>
+        <v>127360820</v>
       </c>
       <c r="B15" t="n">
         <v>57669</v>
@@ -2149,7 +2137,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2159,10 +2147,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560751</v>
+        <v>560582</v>
       </c>
       <c r="R15" t="n">
-        <v>6463687</v>
+        <v>6463723</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2195,11 +2183,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2226,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127354529</v>
+        <v>127359646</v>
       </c>
       <c r="B16" t="n">
-        <v>91350</v>
+        <v>57669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,26 +2220,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2264,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560782</v>
+        <v>560751</v>
       </c>
       <c r="R16" t="n">
-        <v>6463706</v>
+        <v>6463687</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2302,13 +2298,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127360616</v>
+        <v>127359706</v>
       </c>
       <c r="B20" t="n">
-        <v>79647</v>
+        <v>5493</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,26 +2663,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2690,10 +2692,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560704</v>
+        <v>560830</v>
       </c>
       <c r="R20" t="n">
-        <v>6463675</v>
+        <v>6463638</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2875,10 +2877,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127359706</v>
+        <v>127360616</v>
       </c>
       <c r="B22" t="n">
-        <v>5493</v>
+        <v>79647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2886,28 +2888,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560830</v>
+        <v>560704</v>
       </c>
       <c r="R22" t="n">
-        <v>6463638</v>
+        <v>6463675</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127354262</v>
+        <v>127359680</v>
       </c>
       <c r="B24" t="n">
-        <v>57669</v>
+        <v>91370</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,39 +3090,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3130,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560850</v>
+        <v>560809</v>
       </c>
       <c r="R24" t="n">
-        <v>6463659</v>
+        <v>6463646</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3174,6 +3161,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3192,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127360466</v>
+        <v>127355274</v>
       </c>
       <c r="B25" t="n">
-        <v>79647</v>
+        <v>91370</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3203,21 +3191,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3230,10 +3218,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560882</v>
+        <v>560763</v>
       </c>
       <c r="R25" t="n">
-        <v>6463540</v>
+        <v>6463697</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3293,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127359680</v>
+        <v>127354262</v>
       </c>
       <c r="B26" t="n">
-        <v>91370</v>
+        <v>57669</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3304,26 +3292,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3331,10 +3332,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560809</v>
+        <v>560850</v>
       </c>
       <c r="R26" t="n">
-        <v>6463646</v>
+        <v>6463659</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3375,7 +3376,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3394,10 +3394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127355274</v>
+        <v>127360466</v>
       </c>
       <c r="B27" t="n">
-        <v>91370</v>
+        <v>79647</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3405,21 +3405,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560763</v>
+        <v>560882</v>
       </c>
       <c r="R27" t="n">
-        <v>6463697</v>
+        <v>6463540</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3495,32 +3495,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127359655</v>
+        <v>127360687</v>
       </c>
       <c r="B28" t="n">
-        <v>79115</v>
+        <v>79647</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560751</v>
+        <v>560662</v>
       </c>
       <c r="R28" t="n">
-        <v>6463687</v>
+        <v>6463677</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3596,32 +3596,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127359663</v>
+        <v>127359655</v>
       </c>
       <c r="B29" t="n">
-        <v>91370</v>
+        <v>79115</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>6450</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560780</v>
+        <v>560751</v>
       </c>
       <c r="R29" t="n">
-        <v>6463653</v>
+        <v>6463687</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127360687</v>
+        <v>127359663</v>
       </c>
       <c r="B30" t="n">
-        <v>79647</v>
+        <v>91370</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560662</v>
+        <v>560780</v>
       </c>
       <c r="R30" t="n">
-        <v>6463677</v>
+        <v>6463653</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127381942</v>
+        <v>127360220</v>
       </c>
       <c r="B31" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,26 +3809,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3836,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560617</v>
+        <v>560903</v>
       </c>
       <c r="R31" t="n">
-        <v>6463688</v>
+        <v>6463535</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3874,13 +3891,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Bebott bohål</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3899,10 +3920,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127360157</v>
+        <v>127381955</v>
       </c>
       <c r="B32" t="n">
-        <v>91370</v>
+        <v>57669</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,26 +3931,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3937,10 +3971,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560850</v>
+        <v>560617</v>
       </c>
       <c r="R32" t="n">
-        <v>6463569</v>
+        <v>6463688</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3975,13 +4009,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4000,10 +4038,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127360220</v>
+        <v>127381942</v>
       </c>
       <c r="B33" t="n">
-        <v>57669</v>
+        <v>79647</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4011,43 +4049,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4055,10 +4076,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560903</v>
+        <v>560617</v>
       </c>
       <c r="R33" t="n">
-        <v>6463535</v>
+        <v>6463688</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4093,17 +4114,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Bebott bohål</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4122,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127381955</v>
+        <v>127360157</v>
       </c>
       <c r="B34" t="n">
-        <v>57669</v>
+        <v>91370</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4133,39 +4150,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4173,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560617</v>
+        <v>560850</v>
       </c>
       <c r="R34" t="n">
-        <v>6463688</v>
+        <v>6463569</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4211,17 +4215,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4240,38 +4240,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127360190</v>
+        <v>127354652</v>
       </c>
       <c r="B35" t="n">
-        <v>96070</v>
+        <v>91370</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4279,10 +4278,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560897</v>
+        <v>560773</v>
       </c>
       <c r="R35" t="n">
-        <v>6463507</v>
+        <v>6463729</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4342,37 +4341,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127355375</v>
+        <v>127360190</v>
       </c>
       <c r="B36" t="n">
-        <v>79647</v>
+        <v>96070</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560738</v>
+        <v>560897</v>
       </c>
       <c r="R36" t="n">
-        <v>6463703</v>
+        <v>6463507</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4443,10 +4443,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127354652</v>
+        <v>127355375</v>
       </c>
       <c r="B37" t="n">
-        <v>91370</v>
+        <v>79647</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4454,21 +4454,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560773</v>
+        <v>560738</v>
       </c>
       <c r="R37" t="n">
-        <v>6463729</v>
+        <v>6463703</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127355252</v>
       </c>
       <c r="B2" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,38 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127359952</v>
+        <v>127360839</v>
       </c>
       <c r="B3" t="n">
-        <v>97173</v>
+        <v>79647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2604</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560850</v>
+        <v>560571</v>
       </c>
       <c r="R3" t="n">
-        <v>6463588</v>
+        <v>6463719</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,37 +877,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127360839</v>
+        <v>127359952</v>
       </c>
       <c r="B4" t="n">
-        <v>79647</v>
+        <v>97174</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2604</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560571</v>
+        <v>560850</v>
       </c>
       <c r="R4" t="n">
-        <v>6463719</v>
+        <v>6463588</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,7 +982,7 @@
         <v>127355282</v>
       </c>
       <c r="B5" t="n">
-        <v>105506</v>
+        <v>105507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127359945</v>
       </c>
       <c r="B6" t="n">
-        <v>97147</v>
+        <v>97148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127355369</v>
+        <v>127355314</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>91770</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,43 +1434,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102977</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1478,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560738</v>
+        <v>560745</v>
       </c>
       <c r="R9" t="n">
-        <v>6463703</v>
+        <v>6463691</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,6 +1505,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1540,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127355314</v>
+        <v>127355369</v>
       </c>
       <c r="B10" t="n">
-        <v>91769</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,26 +1535,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5420</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1578,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560745</v>
+        <v>560738</v>
       </c>
       <c r="R10" t="n">
-        <v>6463691</v>
+        <v>6463703</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1622,7 +1623,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>127354529</v>
       </c>
       <c r="B14" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>127359699</v>
       </c>
       <c r="B18" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127359706</v>
+        <v>127360616</v>
       </c>
       <c r="B20" t="n">
-        <v>5493</v>
+        <v>79647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,28 +2663,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2692,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560830</v>
+        <v>560704</v>
       </c>
       <c r="R20" t="n">
-        <v>6463638</v>
+        <v>6463675</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2877,10 +2875,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127360616</v>
+        <v>127359706</v>
       </c>
       <c r="B22" t="n">
-        <v>79647</v>
+        <v>5493</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2888,26 +2886,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560704</v>
+        <v>560830</v>
       </c>
       <c r="R22" t="n">
-        <v>6463675</v>
+        <v>6463638</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2981,7 +2981,7 @@
         <v>127359577</v>
       </c>
       <c r="B23" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>127359680</v>
       </c>
       <c r="B24" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127355274</v>
+        <v>127360466</v>
       </c>
       <c r="B25" t="n">
-        <v>91370</v>
+        <v>79647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,21 +3191,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560763</v>
+        <v>560882</v>
       </c>
       <c r="R25" t="n">
-        <v>6463697</v>
+        <v>6463540</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3281,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127354262</v>
+        <v>127355274</v>
       </c>
       <c r="B26" t="n">
-        <v>57669</v>
+        <v>91371</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3292,39 +3292,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3332,10 +3319,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560850</v>
+        <v>560763</v>
       </c>
       <c r="R26" t="n">
-        <v>6463659</v>
+        <v>6463697</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3376,6 +3363,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3394,10 +3382,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127360466</v>
+        <v>127354262</v>
       </c>
       <c r="B27" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3405,26 +3393,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3432,10 +3433,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560882</v>
+        <v>560850</v>
       </c>
       <c r="R27" t="n">
-        <v>6463540</v>
+        <v>6463659</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3476,7 +3477,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3596,32 +3596,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127359655</v>
+        <v>127359663</v>
       </c>
       <c r="B29" t="n">
-        <v>79115</v>
+        <v>91371</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6450</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560751</v>
+        <v>560780</v>
       </c>
       <c r="R29" t="n">
-        <v>6463687</v>
+        <v>6463653</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3697,32 +3697,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127359663</v>
+        <v>127359655</v>
       </c>
       <c r="B30" t="n">
-        <v>91370</v>
+        <v>79115</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6450</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560780</v>
+        <v>560751</v>
       </c>
       <c r="R30" t="n">
-        <v>6463653</v>
+        <v>6463687</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127360220</v>
+        <v>127381942</v>
       </c>
       <c r="B31" t="n">
-        <v>57669</v>
+        <v>79647</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,43 +3809,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3853,10 +3836,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560903</v>
+        <v>560617</v>
       </c>
       <c r="R31" t="n">
-        <v>6463535</v>
+        <v>6463688</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3891,17 +3874,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Bebott bohål</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3920,10 +3899,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127381955</v>
+        <v>127360157</v>
       </c>
       <c r="B32" t="n">
-        <v>57669</v>
+        <v>91371</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3931,39 +3910,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3971,10 +3937,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560617</v>
+        <v>560850</v>
       </c>
       <c r="R32" t="n">
-        <v>6463688</v>
+        <v>6463569</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4009,17 +3975,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4038,10 +4000,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127381942</v>
+        <v>127360220</v>
       </c>
       <c r="B33" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4049,26 +4011,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4076,10 +4055,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560617</v>
+        <v>560903</v>
       </c>
       <c r="R33" t="n">
-        <v>6463688</v>
+        <v>6463535</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4114,13 +4093,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Bebott bohål</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4139,10 +4122,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127360157</v>
+        <v>127381955</v>
       </c>
       <c r="B34" t="n">
-        <v>91370</v>
+        <v>57669</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4150,26 +4133,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4177,10 +4173,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560850</v>
+        <v>560617</v>
       </c>
       <c r="R34" t="n">
-        <v>6463569</v>
+        <v>6463688</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4215,13 +4211,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>127354652</v>
       </c>
       <c r="B35" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4341,38 +4341,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127360190</v>
+        <v>127355375</v>
       </c>
       <c r="B36" t="n">
-        <v>96070</v>
+        <v>79647</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4380,10 +4379,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560897</v>
+        <v>560738</v>
       </c>
       <c r="R36" t="n">
-        <v>6463507</v>
+        <v>6463703</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4443,37 +4442,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127355375</v>
+        <v>127360190</v>
       </c>
       <c r="B37" t="n">
-        <v>79647</v>
+        <v>96071</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560738</v>
+        <v>560897</v>
       </c>
       <c r="R37" t="n">
-        <v>6463703</v>
+        <v>6463507</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4547,7 +4547,7 @@
         <v>127359873</v>
       </c>
       <c r="B38" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>127360842</v>
       </c>
       <c r="B41" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127355252</v>
       </c>
       <c r="B2" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127360839</v>
+        <v>127359952</v>
       </c>
       <c r="B3" t="n">
-        <v>79647</v>
+        <v>97175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>2604</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -814,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560571</v>
+        <v>560850</v>
       </c>
       <c r="R3" t="n">
-        <v>6463719</v>
+        <v>6463588</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,38 +878,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127359952</v>
+        <v>127360839</v>
       </c>
       <c r="B4" t="n">
-        <v>97174</v>
+        <v>79647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2604</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560850</v>
+        <v>560571</v>
       </c>
       <c r="R4" t="n">
-        <v>6463588</v>
+        <v>6463719</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,7 +982,7 @@
         <v>127355282</v>
       </c>
       <c r="B5" t="n">
-        <v>105507</v>
+        <v>105508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127359945</v>
       </c>
       <c r="B6" t="n">
-        <v>97148</v>
+        <v>97149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127355314</v>
+        <v>127355369</v>
       </c>
       <c r="B9" t="n">
-        <v>91770</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,26 +1434,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>102977</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1461,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560745</v>
+        <v>560738</v>
       </c>
       <c r="R9" t="n">
-        <v>6463691</v>
+        <v>6463703</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,7 +1522,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1524,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127355369</v>
+        <v>127355314</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>91771</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1535,43 +1551,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102977</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1579,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560738</v>
+        <v>560745</v>
       </c>
       <c r="R10" t="n">
-        <v>6463703</v>
+        <v>6463691</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1623,6 +1622,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>127354529</v>
       </c>
       <c r="B14" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>127359699</v>
       </c>
       <c r="B18" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127360616</v>
+        <v>127382193</v>
       </c>
       <c r="B20" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,26 +2663,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2690,10 +2707,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560704</v>
+        <v>560809</v>
       </c>
       <c r="R20" t="n">
-        <v>6463675</v>
+        <v>6463640</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2728,13 +2745,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Observerad</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2753,10 +2774,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127382193</v>
+        <v>127359706</v>
       </c>
       <c r="B21" t="n">
-        <v>57669</v>
+        <v>5493</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2764,43 +2785,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>101410</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2808,10 +2814,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560809</v>
+        <v>560830</v>
       </c>
       <c r="R21" t="n">
-        <v>6463640</v>
+        <v>6463638</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2846,17 +2852,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Observerad</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2875,10 +2877,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127359706</v>
+        <v>127360616</v>
       </c>
       <c r="B22" t="n">
-        <v>5493</v>
+        <v>79647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2886,28 +2888,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560830</v>
+        <v>560704</v>
       </c>
       <c r="R22" t="n">
-        <v>6463638</v>
+        <v>6463675</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2981,7 +2981,7 @@
         <v>127359577</v>
       </c>
       <c r="B23" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127359680</v>
+        <v>127360466</v>
       </c>
       <c r="B24" t="n">
-        <v>91371</v>
+        <v>79647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,21 +3090,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560809</v>
+        <v>560882</v>
       </c>
       <c r="R24" t="n">
-        <v>6463646</v>
+        <v>6463540</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127360466</v>
+        <v>127359680</v>
       </c>
       <c r="B25" t="n">
-        <v>79647</v>
+        <v>91372</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,21 +3191,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560882</v>
+        <v>560809</v>
       </c>
       <c r="R25" t="n">
-        <v>6463540</v>
+        <v>6463646</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3284,7 +3284,7 @@
         <v>127355274</v>
       </c>
       <c r="B26" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,10 +3495,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127360687</v>
+        <v>127359663</v>
       </c>
       <c r="B28" t="n">
-        <v>79647</v>
+        <v>91372</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3506,21 +3506,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560662</v>
+        <v>560780</v>
       </c>
       <c r="R28" t="n">
-        <v>6463677</v>
+        <v>6463653</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127359663</v>
+        <v>127360687</v>
       </c>
       <c r="B29" t="n">
-        <v>91371</v>
+        <v>79647</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560780</v>
+        <v>560662</v>
       </c>
       <c r="R29" t="n">
-        <v>6463653</v>
+        <v>6463677</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3902,7 +3902,7 @@
         <v>127360157</v>
       </c>
       <c r="B32" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4240,10 +4240,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127354652</v>
+        <v>127355375</v>
       </c>
       <c r="B35" t="n">
-        <v>91371</v>
+        <v>79647</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4251,21 +4251,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560773</v>
+        <v>560738</v>
       </c>
       <c r="R35" t="n">
-        <v>6463729</v>
+        <v>6463703</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4341,37 +4341,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127355375</v>
+        <v>127360190</v>
       </c>
       <c r="B36" t="n">
-        <v>79647</v>
+        <v>96072</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4379,10 +4380,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560738</v>
+        <v>560897</v>
       </c>
       <c r="R36" t="n">
-        <v>6463703</v>
+        <v>6463507</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4442,38 +4443,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127360190</v>
+        <v>127354652</v>
       </c>
       <c r="B37" t="n">
-        <v>96071</v>
+        <v>91372</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560897</v>
+        <v>560773</v>
       </c>
       <c r="R37" t="n">
-        <v>6463507</v>
+        <v>6463729</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4544,10 +4544,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127359873</v>
+        <v>127354580</v>
       </c>
       <c r="B38" t="n">
-        <v>91371</v>
+        <v>57669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,26 +4555,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4582,10 +4595,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560879</v>
+        <v>560782</v>
       </c>
       <c r="R38" t="n">
-        <v>6463611</v>
+        <v>6463706</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4620,13 +4633,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4645,10 +4662,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127354580</v>
+        <v>127359873</v>
       </c>
       <c r="B39" t="n">
-        <v>57669</v>
+        <v>91372</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4656,39 +4673,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4696,10 +4700,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560782</v>
+        <v>560879</v>
       </c>
       <c r="R39" t="n">
-        <v>6463706</v>
+        <v>6463611</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4734,17 +4738,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4883,7 +4883,7 @@
         <v>127360842</v>
       </c>
       <c r="B41" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127355369</v>
+        <v>127355314</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>91771</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,43 +1434,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102977</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1478,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560738</v>
+        <v>560745</v>
       </c>
       <c r="R9" t="n">
-        <v>6463703</v>
+        <v>6463691</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,6 +1505,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1540,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127355314</v>
+        <v>127355369</v>
       </c>
       <c r="B10" t="n">
-        <v>91771</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,26 +1535,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5420</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1578,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560745</v>
+        <v>560738</v>
       </c>
       <c r="R10" t="n">
-        <v>6463691</v>
+        <v>6463703</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1622,7 +1623,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127359702</v>
+        <v>127359699</v>
       </c>
       <c r="B17" t="n">
-        <v>79647</v>
+        <v>91372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,21 +2338,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2403,6 +2403,11 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Flera på samma träd</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2428,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127359699</v>
+        <v>127359702</v>
       </c>
       <c r="B18" t="n">
-        <v>91372</v>
+        <v>79647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2439,21 +2444,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2504,11 +2509,6 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Flera på samma träd</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127382193</v>
+        <v>127360616</v>
       </c>
       <c r="B20" t="n">
-        <v>57669</v>
+        <v>79647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,43 +2663,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2707,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560809</v>
+        <v>560704</v>
       </c>
       <c r="R20" t="n">
-        <v>6463640</v>
+        <v>6463675</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2745,17 +2728,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Observerad</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2774,10 +2753,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127359706</v>
+        <v>127382193</v>
       </c>
       <c r="B21" t="n">
-        <v>5493</v>
+        <v>57669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,28 +2764,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101410</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2814,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560830</v>
+        <v>560809</v>
       </c>
       <c r="R21" t="n">
-        <v>6463638</v>
+        <v>6463640</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2852,13 +2846,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Observerad</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2877,10 +2875,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127360616</v>
+        <v>127359706</v>
       </c>
       <c r="B22" t="n">
-        <v>79647</v>
+        <v>5493</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2888,26 +2886,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560704</v>
+        <v>560830</v>
       </c>
       <c r="R22" t="n">
-        <v>6463675</v>
+        <v>6463638</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127360466</v>
+        <v>127354262</v>
       </c>
       <c r="B24" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,26 +3090,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3117,10 +3130,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560882</v>
+        <v>560850</v>
       </c>
       <c r="R24" t="n">
-        <v>6463540</v>
+        <v>6463659</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3161,7 +3174,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3382,10 +3394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127354262</v>
+        <v>127360466</v>
       </c>
       <c r="B27" t="n">
-        <v>57669</v>
+        <v>79647</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3393,39 +3405,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3433,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560850</v>
+        <v>560882</v>
       </c>
       <c r="R27" t="n">
-        <v>6463659</v>
+        <v>6463540</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3477,6 +3476,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127381942</v>
+        <v>127360157</v>
       </c>
       <c r="B31" t="n">
-        <v>79647</v>
+        <v>91372</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3809,21 +3809,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560617</v>
+        <v>560850</v>
       </c>
       <c r="R31" t="n">
-        <v>6463688</v>
+        <v>6463569</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127360157</v>
+        <v>127360220</v>
       </c>
       <c r="B32" t="n">
-        <v>91372</v>
+        <v>57669</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,26 +3910,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3937,10 +3954,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560850</v>
+        <v>560903</v>
       </c>
       <c r="R32" t="n">
-        <v>6463569</v>
+        <v>6463535</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3975,13 +3992,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Bebott bohål</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4000,7 +4021,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127360220</v>
+        <v>127381955</v>
       </c>
       <c r="B33" t="n">
         <v>57669</v>
@@ -4038,11 +4059,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4055,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560903</v>
+        <v>560617</v>
       </c>
       <c r="R33" t="n">
-        <v>6463535</v>
+        <v>6463688</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4095,7 +4112,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Bebott bohål</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4122,10 +4139,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127381955</v>
+        <v>127381942</v>
       </c>
       <c r="B34" t="n">
-        <v>57669</v>
+        <v>79647</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4133,39 +4150,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4211,17 +4215,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4240,10 +4240,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127355375</v>
+        <v>127354652</v>
       </c>
       <c r="B35" t="n">
-        <v>79647</v>
+        <v>91372</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4251,21 +4251,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560738</v>
+        <v>560773</v>
       </c>
       <c r="R35" t="n">
-        <v>6463703</v>
+        <v>6463729</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4341,38 +4341,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127360190</v>
+        <v>127355375</v>
       </c>
       <c r="B36" t="n">
-        <v>96072</v>
+        <v>79647</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4380,10 +4379,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560897</v>
+        <v>560738</v>
       </c>
       <c r="R36" t="n">
-        <v>6463507</v>
+        <v>6463703</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4443,37 +4442,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127354652</v>
+        <v>127360190</v>
       </c>
       <c r="B37" t="n">
-        <v>91372</v>
+        <v>96072</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560773</v>
+        <v>560897</v>
       </c>
       <c r="R37" t="n">
-        <v>6463729</v>
+        <v>6463507</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4544,10 +4544,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127354580</v>
+        <v>127359873</v>
       </c>
       <c r="B38" t="n">
-        <v>57669</v>
+        <v>91372</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,39 +4555,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4595,10 +4582,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560782</v>
+        <v>560879</v>
       </c>
       <c r="R38" t="n">
-        <v>6463706</v>
+        <v>6463611</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4633,17 +4620,13 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4662,10 +4645,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127359873</v>
+        <v>127354580</v>
       </c>
       <c r="B39" t="n">
-        <v>91372</v>
+        <v>57669</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4673,26 +4656,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4700,10 +4696,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560879</v>
+        <v>560782</v>
       </c>
       <c r="R39" t="n">
-        <v>6463611</v>
+        <v>6463706</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4738,13 +4734,17 @@
           <t>2025-07-30</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5455,6 +5455,1170 @@
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128726622</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57686</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Risten-Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>560808</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6463696</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128726575</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57686</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Risten-Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>560712</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6463666</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Även äldre spår</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128726497</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79708</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Risten-Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>560665</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6463715</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128726928</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91486</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Risten-Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>560855</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6463639</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>En ganska lien fruktkropp som är lätt att missa om man inte kollar noga.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128726409</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91450</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Risten-Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>560769</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6463750</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128726434</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91486</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Risten-Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>560783</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6463732</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128726614</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98588</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Risten-Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>560788</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6463689</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128726506</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57686</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Risten-Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>560665</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6463715</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Även äldre spår</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128726518</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79708</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Risten-Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>560703</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6463666</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128726475</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Risten-Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>560748</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6463709</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta revir. Reviret utgörs främst av den gamla kontinuitetsskogen men även av anslutande yngre skogsområden.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128726511</v>
+      </c>
+      <c r="B56" t="n">
+        <v>89398</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>2979</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Lömsk flugsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Amanita phalloides</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Link</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Risten-Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>560665</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6463715</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -6088,7 +6088,7 @@
         <v>128726614</v>
       </c>
       <c r="B52" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -5776,7 +5776,7 @@
         <v>128726928</v>
       </c>
       <c r="B49" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>128726409</v>
       </c>
       <c r="B50" t="n">
-        <v>91450</v>
+        <v>91451</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>128726434</v>
       </c>
       <c r="B51" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>128726614</v>
       </c>
       <c r="B52" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6402,50 +6402,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128726475</v>
+        <v>128726511</v>
       </c>
       <c r="B55" t="n">
-        <v>57849</v>
+        <v>89398</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>2979</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lömsk flugsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Amanita phalloides</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Link</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6453,10 +6440,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>560748</v>
+        <v>560665</v>
       </c>
       <c r="R55" t="n">
-        <v>6463709</v>
+        <v>6463715</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6491,17 +6478,13 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta revir. Reviret utgörs främst av den gamla kontinuitetsskogen men även av anslutande yngre skogsområden.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6520,37 +6503,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128726511</v>
+        <v>128726475</v>
       </c>
       <c r="B56" t="n">
-        <v>89398</v>
+        <v>57849</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2979</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lömsk flugsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Amanita phalloides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Link</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6558,10 +6554,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>560665</v>
+        <v>560748</v>
       </c>
       <c r="R56" t="n">
-        <v>6463715</v>
+        <v>6463709</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6596,13 +6592,17 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta revir. Reviret utgörs främst av den gamla kontinuitetsskogen men även av anslutande yngre skogsområden.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -5460,7 +5460,7 @@
         <v>128726622</v>
       </c>
       <c r="B46" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>128726575</v>
       </c>
       <c r="B47" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>128726497</v>
       </c>
       <c r="B48" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>128726928</v>
       </c>
       <c r="B49" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>128726409</v>
       </c>
       <c r="B50" t="n">
-        <v>91451</v>
+        <v>91478</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>128726434</v>
       </c>
       <c r="B51" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>128726614</v>
       </c>
       <c r="B52" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>128726506</v>
       </c>
       <c r="B53" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>128726518</v>
       </c>
       <c r="B54" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6402,37 +6402,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128726511</v>
+        <v>128726475</v>
       </c>
       <c r="B55" t="n">
-        <v>89398</v>
+        <v>57876</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2979</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lömsk flugsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Amanita phalloides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Link</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6440,10 +6453,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>560665</v>
+        <v>560748</v>
       </c>
       <c r="R55" t="n">
-        <v>6463715</v>
+        <v>6463709</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6478,13 +6491,17 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta revir. Reviret utgörs främst av den gamla kontinuitetsskogen men även av anslutande yngre skogsområden.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6503,50 +6520,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128726475</v>
+        <v>128726511</v>
       </c>
       <c r="B56" t="n">
-        <v>57849</v>
+        <v>89425</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>2979</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lömsk flugsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Amanita phalloides</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Link</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6554,10 +6558,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>560748</v>
+        <v>560665</v>
       </c>
       <c r="R56" t="n">
-        <v>6463709</v>
+        <v>6463715</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6592,17 +6596,13 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta revir. Reviret utgörs främst av den gamla kontinuitetsskogen men även av anslutande yngre skogsområden.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -5675,7 +5675,7 @@
         <v>128726497</v>
       </c>
       <c r="B48" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>128726928</v>
       </c>
       <c r="B49" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>128726409</v>
       </c>
       <c r="B50" t="n">
-        <v>91478</v>
+        <v>91483</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>128726434</v>
       </c>
       <c r="B51" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>128726614</v>
       </c>
       <c r="B52" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>128726518</v>
       </c>
       <c r="B54" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         <v>128726511</v>
       </c>
       <c r="B56" t="n">
-        <v>89425</v>
+        <v>89430</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -5776,7 +5776,7 @@
         <v>128726928</v>
       </c>
       <c r="B49" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>128726409</v>
       </c>
       <c r="B50" t="n">
-        <v>91483</v>
+        <v>91488</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>128726434</v>
       </c>
       <c r="B51" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>128726614</v>
       </c>
       <c r="B52" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6402,50 +6402,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128726475</v>
+        <v>128726511</v>
       </c>
       <c r="B55" t="n">
-        <v>57876</v>
+        <v>89435</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>2979</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lömsk flugsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Amanita phalloides</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Link</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6453,10 +6440,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>560748</v>
+        <v>560665</v>
       </c>
       <c r="R55" t="n">
-        <v>6463709</v>
+        <v>6463715</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6491,17 +6478,13 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta revir. Reviret utgörs främst av den gamla kontinuitetsskogen men även av anslutande yngre skogsområden.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6520,37 +6503,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128726511</v>
+        <v>128726475</v>
       </c>
       <c r="B56" t="n">
-        <v>89430</v>
+        <v>57876</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2979</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lömsk flugsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Amanita phalloides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Link</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6558,10 +6554,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>560665</v>
+        <v>560748</v>
       </c>
       <c r="R56" t="n">
-        <v>6463715</v>
+        <v>6463709</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6596,13 +6592,17 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta revir. Reviret utgörs främst av den gamla kontinuitetsskogen men även av anslutande yngre skogsområden.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -5460,7 +5460,7 @@
         <v>128726622</v>
       </c>
       <c r="B46" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>128726575</v>
       </c>
       <c r="B47" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>128726497</v>
       </c>
       <c r="B48" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>128726928</v>
       </c>
       <c r="B49" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>128726409</v>
       </c>
       <c r="B50" t="n">
-        <v>91488</v>
+        <v>91492</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>128726434</v>
       </c>
       <c r="B51" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>128726614</v>
       </c>
       <c r="B52" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>128726506</v>
       </c>
       <c r="B53" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>128726518</v>
       </c>
       <c r="B54" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>128726511</v>
       </c>
       <c r="B55" t="n">
-        <v>89435</v>
+        <v>89439</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>128726475</v>
       </c>
       <c r="B56" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -5460,7 +5460,7 @@
         <v>128726622</v>
       </c>
       <c r="B46" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>128726575</v>
       </c>
       <c r="B47" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>128726497</v>
       </c>
       <c r="B48" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>128726928</v>
       </c>
       <c r="B49" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>128726409</v>
       </c>
       <c r="B50" t="n">
-        <v>91492</v>
+        <v>91497</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>128726434</v>
       </c>
       <c r="B51" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>128726614</v>
       </c>
       <c r="B52" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>128726506</v>
       </c>
       <c r="B53" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>128726518</v>
       </c>
       <c r="B54" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>128726511</v>
       </c>
       <c r="B55" t="n">
-        <v>89439</v>
+        <v>89444</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>128726475</v>
       </c>
       <c r="B56" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -5776,7 +5776,7 @@
         <v>128726928</v>
       </c>
       <c r="B49" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>128726409</v>
       </c>
       <c r="B50" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>128726434</v>
       </c>
       <c r="B51" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>128726614</v>
       </c>
       <c r="B52" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>128726511</v>
       </c>
       <c r="B55" t="n">
-        <v>89451</v>
+        <v>89454</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -5675,7 +5675,7 @@
         <v>128726497</v>
       </c>
       <c r="B48" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>128726928</v>
       </c>
       <c r="B49" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>128726409</v>
       </c>
       <c r="B50" t="n">
-        <v>91507</v>
+        <v>91510</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>128726434</v>
       </c>
       <c r="B51" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>128726614</v>
       </c>
       <c r="B52" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>128726518</v>
       </c>
       <c r="B54" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>128726511</v>
       </c>
       <c r="B55" t="n">
-        <v>89454</v>
+        <v>89457</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -6402,37 +6402,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128726511</v>
+        <v>128726475</v>
       </c>
       <c r="B55" t="n">
-        <v>89457</v>
+        <v>57883</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2979</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lömsk flugsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Amanita phalloides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Link</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6440,10 +6453,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>560665</v>
+        <v>560748</v>
       </c>
       <c r="R55" t="n">
-        <v>6463715</v>
+        <v>6463709</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6478,13 +6491,17 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta revir. Reviret utgörs främst av den gamla kontinuitetsskogen men även av anslutande yngre skogsområden.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6503,50 +6520,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128726475</v>
+        <v>128726511</v>
       </c>
       <c r="B56" t="n">
-        <v>57883</v>
+        <v>89457</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>2979</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lömsk flugsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Amanita phalloides</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Link</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6554,10 +6558,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>560748</v>
+        <v>560665</v>
       </c>
       <c r="R56" t="n">
-        <v>6463709</v>
+        <v>6463715</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6592,17 +6596,13 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta revir. Reviret utgörs främst av den gamla kontinuitetsskogen men även av anslutande yngre skogsområden.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -5460,7 +5460,7 @@
         <v>128726622</v>
       </c>
       <c r="B46" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>128726575</v>
       </c>
       <c r="B47" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>128726497</v>
       </c>
       <c r="B48" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>128726928</v>
       </c>
       <c r="B49" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>128726409</v>
       </c>
       <c r="B50" t="n">
-        <v>91510</v>
+        <v>91517</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>128726434</v>
       </c>
       <c r="B51" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>128726614</v>
       </c>
       <c r="B52" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>128726506</v>
       </c>
       <c r="B53" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>128726518</v>
       </c>
       <c r="B54" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6402,50 +6402,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128726475</v>
+        <v>128726511</v>
       </c>
       <c r="B55" t="n">
-        <v>57883</v>
+        <v>89461</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>2979</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lömsk flugsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Amanita phalloides</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Link</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6453,10 +6440,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>560748</v>
+        <v>560665</v>
       </c>
       <c r="R55" t="n">
-        <v>6463709</v>
+        <v>6463715</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6491,17 +6478,13 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta revir. Reviret utgörs främst av den gamla kontinuitetsskogen men även av anslutande yngre skogsområden.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6520,37 +6503,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128726511</v>
+        <v>128726475</v>
       </c>
       <c r="B56" t="n">
-        <v>89457</v>
+        <v>57885</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2979</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lömsk flugsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Amanita phalloides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Link</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6558,10 +6554,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>560665</v>
+        <v>560748</v>
       </c>
       <c r="R56" t="n">
-        <v>6463715</v>
+        <v>6463709</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6596,13 +6592,17 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta revir. Reviret utgörs främst av den gamla kontinuitetsskogen men även av anslutande yngre skogsområden.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -5460,7 +5460,7 @@
         <v>128726622</v>
       </c>
       <c r="B46" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>128726575</v>
       </c>
       <c r="B47" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>128726497</v>
       </c>
       <c r="B48" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>128726928</v>
       </c>
       <c r="B49" t="n">
-        <v>91553</v>
+        <v>91562</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>128726409</v>
       </c>
       <c r="B50" t="n">
-        <v>91517</v>
+        <v>91526</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>128726434</v>
       </c>
       <c r="B51" t="n">
-        <v>91553</v>
+        <v>91562</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>128726614</v>
       </c>
       <c r="B52" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>128726506</v>
       </c>
       <c r="B53" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>128726518</v>
       </c>
       <c r="B54" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>128726511</v>
       </c>
       <c r="B55" t="n">
-        <v>89461</v>
+        <v>89470</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>128726475</v>
       </c>
       <c r="B56" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -6402,37 +6402,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128726511</v>
+        <v>128726475</v>
       </c>
       <c r="B55" t="n">
-        <v>89470</v>
+        <v>57887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2979</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lömsk flugsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Amanita phalloides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Link</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6440,10 +6453,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>560665</v>
+        <v>560748</v>
       </c>
       <c r="R55" t="n">
-        <v>6463715</v>
+        <v>6463709</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6478,13 +6491,17 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta revir. Reviret utgörs främst av den gamla kontinuitetsskogen men även av anslutande yngre skogsområden.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6503,50 +6520,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128726475</v>
+        <v>128726511</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>89470</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>2979</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lömsk flugsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Amanita phalloides</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Link</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6554,10 +6558,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>560748</v>
+        <v>560665</v>
       </c>
       <c r="R56" t="n">
-        <v>6463709</v>
+        <v>6463715</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6592,17 +6596,13 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta revir. Reviret utgörs främst av den gamla kontinuitetsskogen men även av anslutande yngre skogsområden.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -1186,7 +1186,7 @@
         <v>127354741</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>127355148</v>
       </c>
       <c r="B8" t="n">
-        <v>57897</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>127359896</v>
       </c>
       <c r="B11" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127360624</v>
       </c>
       <c r="B12" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>127359646</v>
       </c>
       <c r="B16" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>127355403</v>
       </c>
       <c r="B19" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>127382193</v>
       </c>
       <c r="B21" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>127360220</v>
       </c>
       <c r="B32" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>127381955</v>
       </c>
       <c r="B33" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>127360176</v>
       </c>
       <c r="B40" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>127355339</v>
       </c>
       <c r="B42" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>127381965</v>
       </c>
       <c r="B44" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>127360121</v>
       </c>
       <c r="B45" t="n">
-        <v>57897</v>
+        <v>57899</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>131269236</v>
       </c>
       <c r="B57" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>131269217</v>
       </c>
       <c r="B58" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>131269222</v>
       </c>
       <c r="B59" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -1186,7 +1186,7 @@
         <v>127354741</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>127355148</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>127359896</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127360624</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>127359646</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>127355403</v>
       </c>
       <c r="B19" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>127382193</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>127360220</v>
       </c>
       <c r="B32" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>127381955</v>
       </c>
       <c r="B33" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>127360176</v>
       </c>
       <c r="B40" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>127355339</v>
       </c>
       <c r="B42" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>127381965</v>
       </c>
       <c r="B44" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>127360121</v>
       </c>
       <c r="B45" t="n">
-        <v>57899</v>
+        <v>57900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>131269236</v>
       </c>
       <c r="B57" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>131269217</v>
       </c>
       <c r="B58" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>131269222</v>
       </c>
       <c r="B59" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -1186,7 +1186,7 @@
         <v>127354741</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>127355148</v>
       </c>
       <c r="B8" t="n">
-        <v>57900</v>
+        <v>57901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>127359896</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127360624</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>127359646</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>127355403</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>127382193</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>127360220</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>127381955</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>127360176</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>127355339</v>
       </c>
       <c r="B42" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>127381965</v>
       </c>
       <c r="B44" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>127360121</v>
       </c>
       <c r="B45" t="n">
-        <v>57900</v>
+        <v>57901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>131269217</v>
       </c>
       <c r="B58" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>131269222</v>
       </c>
       <c r="B59" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -1186,7 +1186,7 @@
         <v>127354741</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>127355148</v>
       </c>
       <c r="B8" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>127359896</v>
       </c>
       <c r="B11" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127360624</v>
       </c>
       <c r="B12" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>127359646</v>
       </c>
       <c r="B16" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>127355403</v>
       </c>
       <c r="B19" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>127382193</v>
       </c>
       <c r="B21" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>127360220</v>
       </c>
       <c r="B32" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>127381955</v>
       </c>
       <c r="B33" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>127360176</v>
       </c>
       <c r="B40" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>127355339</v>
       </c>
       <c r="B42" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>127381965</v>
       </c>
       <c r="B44" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>127360121</v>
       </c>
       <c r="B45" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>131269236</v>
       </c>
       <c r="B57" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>131269217</v>
       </c>
       <c r="B58" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>131269222</v>
       </c>
       <c r="B59" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -1186,7 +1186,7 @@
         <v>127354741</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>127355148</v>
       </c>
       <c r="B8" t="n">
-        <v>57904</v>
+        <v>57905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>127359896</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127360624</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>127359646</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>127355403</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>127382193</v>
       </c>
       <c r="B21" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>127360220</v>
       </c>
       <c r="B32" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>127381955</v>
       </c>
       <c r="B33" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>127360176</v>
       </c>
       <c r="B40" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>127355339</v>
       </c>
       <c r="B42" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>127381965</v>
       </c>
       <c r="B44" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>127360121</v>
       </c>
       <c r="B45" t="n">
-        <v>57904</v>
+        <v>57905</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>131269236</v>
       </c>
       <c r="B57" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>131269217</v>
       </c>
       <c r="B58" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>131269222</v>
       </c>
       <c r="B59" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1186,7 +1186,7 @@
         <v>127354741</v>
       </c>
       <c r="B7" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>127355148</v>
       </c>
       <c r="B8" t="n">
-        <v>57905</v>
+        <v>57911</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>127359896</v>
       </c>
       <c r="B11" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127360624</v>
       </c>
       <c r="B12" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>127359646</v>
       </c>
       <c r="B16" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>127355403</v>
       </c>
       <c r="B19" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>127382193</v>
       </c>
       <c r="B21" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>127360220</v>
       </c>
       <c r="B32" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>127381955</v>
       </c>
       <c r="B33" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>127360176</v>
       </c>
       <c r="B40" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>127355339</v>
       </c>
       <c r="B42" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>127381965</v>
       </c>
       <c r="B44" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>127360121</v>
       </c>
       <c r="B45" t="n">
-        <v>57905</v>
+        <v>57911</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>131269236</v>
       </c>
       <c r="B57" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>131269217</v>
       </c>
       <c r="B58" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>131269222</v>
       </c>
       <c r="B59" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6970,6 +6970,629 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>131634080</v>
+      </c>
+      <c r="B60" t="n">
+        <v>4986</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100307</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blompraktbagge</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Anthaxia morio</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Barrskog vid Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>560803</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6463627</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>William Rosén, Fanny Nyberg</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>131634505</v>
+      </c>
+      <c r="B61" t="n">
+        <v>93115</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Barrskog vid Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>560686</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6463693</v>
+      </c>
+      <c r="S61" t="n">
+        <v>8</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>William Rosén, Fanny Nyberg</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>131634094</v>
+      </c>
+      <c r="B62" t="n">
+        <v>101237</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Barrskog vid Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>560764</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6463672</v>
+      </c>
+      <c r="S62" t="n">
+        <v>9</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>William Rosén, Fanny Nyberg</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>131634130</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92266</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Barrskog vid Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>560631</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6463690</v>
+      </c>
+      <c r="S63" t="n">
+        <v>7</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>William Rosén, Fanny Nyberg</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>131633996</v>
+      </c>
+      <c r="B64" t="n">
+        <v>92251</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Barrskog vid Mulstad, Ög</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>560686</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6463693</v>
+      </c>
+      <c r="S64" t="n">
+        <v>8</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>William Rosén, Fanny Nyberg</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -6973,10 +6973,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131634080</v>
+        <v>131634505</v>
       </c>
       <c r="B60" t="n">
-        <v>4986</v>
+        <v>93115</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6984,52 +6984,52 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100307</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blompraktbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anthaxia morio</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>560803</v>
+        <v>560686</v>
       </c>
       <c r="R60" t="n">
-        <v>6463627</v>
+        <v>6463693</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7077,6 +7077,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7095,10 +7096,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131634505</v>
+        <v>131634080</v>
       </c>
       <c r="B61" t="n">
-        <v>93115</v>
+        <v>4986</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7106,52 +7107,52 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>100307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blompraktbagge</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthaxia morio</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>560686</v>
+        <v>560803</v>
       </c>
       <c r="R61" t="n">
-        <v>6463693</v>
+        <v>6463627</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7180,7 +7181,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7190,7 +7191,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7199,7 +7200,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -6973,10 +6973,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131634505</v>
+        <v>131634080</v>
       </c>
       <c r="B60" t="n">
-        <v>93115</v>
+        <v>4986</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6984,52 +6984,52 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>100307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blompraktbagge</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthaxia morio</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>560686</v>
+        <v>560803</v>
       </c>
       <c r="R60" t="n">
-        <v>6463693</v>
+        <v>6463627</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7077,7 +7077,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7096,10 +7095,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131634080</v>
+        <v>131634505</v>
       </c>
       <c r="B61" t="n">
-        <v>4986</v>
+        <v>93115</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7107,52 +7106,52 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100307</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blompraktbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anthaxia morio</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>560803</v>
+        <v>560686</v>
       </c>
       <c r="R61" t="n">
-        <v>6463627</v>
+        <v>6463693</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7181,7 +7180,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7191,7 +7190,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7200,6 +7199,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -7098,7 +7098,7 @@
         <v>131634505</v>
       </c>
       <c r="B61" t="n">
-        <v>93115</v>
+        <v>93116</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>131634094</v>
       </c>
       <c r="B62" t="n">
-        <v>101237</v>
+        <v>101238</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>131634130</v>
       </c>
       <c r="B63" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>131633996</v>
       </c>
       <c r="B64" t="n">
-        <v>92251</v>
+        <v>92252</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -1186,7 +1186,7 @@
         <v>127354741</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>127355148</v>
       </c>
       <c r="B8" t="n">
-        <v>57911</v>
+        <v>57912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>127359896</v>
       </c>
       <c r="B11" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127360624</v>
       </c>
       <c r="B12" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>127359646</v>
       </c>
       <c r="B16" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>127355403</v>
       </c>
       <c r="B19" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>127382193</v>
       </c>
       <c r="B21" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>127360220</v>
       </c>
       <c r="B32" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>127381955</v>
       </c>
       <c r="B33" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>127360176</v>
       </c>
       <c r="B40" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>127355339</v>
       </c>
       <c r="B42" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>127381965</v>
       </c>
       <c r="B44" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>127360121</v>
       </c>
       <c r="B45" t="n">
-        <v>57911</v>
+        <v>57912</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>131269236</v>
       </c>
       <c r="B57" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>131269217</v>
       </c>
       <c r="B58" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>131269222</v>
       </c>
       <c r="B59" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6973,10 +6973,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131634080</v>
+        <v>131634505</v>
       </c>
       <c r="B60" t="n">
-        <v>4986</v>
+        <v>93117</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6984,52 +6984,52 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100307</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blompraktbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anthaxia morio</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>560803</v>
+        <v>560686</v>
       </c>
       <c r="R60" t="n">
-        <v>6463627</v>
+        <v>6463693</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7077,6 +7077,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7095,10 +7096,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131634505</v>
+        <v>131634080</v>
       </c>
       <c r="B61" t="n">
-        <v>93116</v>
+        <v>4987</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7106,52 +7107,52 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>100307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blompraktbagge</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthaxia morio</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>560686</v>
+        <v>560803</v>
       </c>
       <c r="R61" t="n">
-        <v>6463693</v>
+        <v>6463627</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7180,7 +7181,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7190,7 +7191,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7199,7 +7200,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7221,7 +7221,7 @@
         <v>131634094</v>
       </c>
       <c r="B62" t="n">
-        <v>101238</v>
+        <v>101239</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>131634130</v>
       </c>
       <c r="B63" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>131633996</v>
       </c>
       <c r="B64" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -1186,7 +1186,7 @@
         <v>127354741</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>127355148</v>
       </c>
       <c r="B8" t="n">
-        <v>57912</v>
+        <v>57915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>127359896</v>
       </c>
       <c r="B11" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127360624</v>
       </c>
       <c r="B12" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>127359646</v>
       </c>
       <c r="B16" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>127355403</v>
       </c>
       <c r="B19" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>127382193</v>
       </c>
       <c r="B21" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>127360220</v>
       </c>
       <c r="B32" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>127381955</v>
       </c>
       <c r="B33" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>127360176</v>
       </c>
       <c r="B40" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>127355339</v>
       </c>
       <c r="B42" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>127381965</v>
       </c>
       <c r="B44" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>127360121</v>
       </c>
       <c r="B45" t="n">
-        <v>57912</v>
+        <v>57915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>131269236</v>
       </c>
       <c r="B57" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>131269217</v>
       </c>
       <c r="B58" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>131269222</v>
       </c>
       <c r="B59" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>131634505</v>
       </c>
       <c r="B60" t="n">
-        <v>93117</v>
+        <v>93120</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>131634094</v>
       </c>
       <c r="B62" t="n">
-        <v>101239</v>
+        <v>101242</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>131634130</v>
       </c>
       <c r="B63" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>131633996</v>
       </c>
       <c r="B64" t="n">
-        <v>92253</v>
+        <v>92256</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -7221,7 +7221,7 @@
         <v>131634094</v>
       </c>
       <c r="B62" t="n">
-        <v>101242</v>
+        <v>101243</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -6973,10 +6973,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131634505</v>
+        <v>131634080</v>
       </c>
       <c r="B60" t="n">
-        <v>93120</v>
+        <v>4987</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6984,52 +6984,52 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>100307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blompraktbagge</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthaxia morio</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>560686</v>
+        <v>560803</v>
       </c>
       <c r="R60" t="n">
-        <v>6463693</v>
+        <v>6463627</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7077,7 +7077,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7096,10 +7095,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131634080</v>
+        <v>131634505</v>
       </c>
       <c r="B61" t="n">
-        <v>4987</v>
+        <v>93120</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7107,52 +7106,52 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100307</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blompraktbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anthaxia morio</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>560803</v>
+        <v>560686</v>
       </c>
       <c r="R61" t="n">
-        <v>6463627</v>
+        <v>6463693</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7181,7 +7180,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7191,7 +7190,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7200,6 +7199,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -6973,10 +6973,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131634080</v>
+        <v>131634505</v>
       </c>
       <c r="B60" t="n">
-        <v>4987</v>
+        <v>93120</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6984,52 +6984,52 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100307</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blompraktbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anthaxia morio</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>560803</v>
+        <v>560686</v>
       </c>
       <c r="R60" t="n">
-        <v>6463627</v>
+        <v>6463693</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7077,6 +7077,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7095,10 +7096,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131634505</v>
+        <v>131634080</v>
       </c>
       <c r="B61" t="n">
-        <v>93120</v>
+        <v>4987</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7106,52 +7107,52 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>100307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blompraktbagge</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthaxia morio</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>560686</v>
+        <v>560803</v>
       </c>
       <c r="R61" t="n">
-        <v>6463693</v>
+        <v>6463627</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7180,7 +7181,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7190,7 +7191,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7199,7 +7200,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -1186,7 +1186,7 @@
         <v>127354741</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>127355148</v>
       </c>
       <c r="B8" t="n">
-        <v>57915</v>
+        <v>57917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>127359896</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>127360624</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>127359646</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>127355403</v>
       </c>
       <c r="B19" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>127382193</v>
       </c>
       <c r="B21" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>127360220</v>
       </c>
       <c r="B32" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>127381955</v>
       </c>
       <c r="B33" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>127360176</v>
       </c>
       <c r="B40" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>127355339</v>
       </c>
       <c r="B42" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>127381965</v>
       </c>
       <c r="B44" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>127360121</v>
       </c>
       <c r="B45" t="n">
-        <v>57915</v>
+        <v>57917</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>131269222</v>
       </c>
       <c r="B59" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>131634505</v>
       </c>
       <c r="B60" t="n">
-        <v>93120</v>
+        <v>93126</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>131634094</v>
       </c>
       <c r="B62" t="n">
-        <v>101243</v>
+        <v>101249</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>131634130</v>
       </c>
       <c r="B63" t="n">
-        <v>92271</v>
+        <v>92277</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>131633996</v>
       </c>
       <c r="B64" t="n">
-        <v>92256</v>
+        <v>92262</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -6973,10 +6973,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131634505</v>
+        <v>131634080</v>
       </c>
       <c r="B60" t="n">
-        <v>93126</v>
+        <v>4987</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6984,52 +6984,52 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>100307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blompraktbagge</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthaxia morio</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>560686</v>
+        <v>560803</v>
       </c>
       <c r="R60" t="n">
-        <v>6463693</v>
+        <v>6463627</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7077,7 +7077,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7096,10 +7095,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131634080</v>
+        <v>131634505</v>
       </c>
       <c r="B61" t="n">
-        <v>4987</v>
+        <v>93126</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7107,52 +7106,52 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100307</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blompraktbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anthaxia morio</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>560803</v>
+        <v>560686</v>
       </c>
       <c r="R61" t="n">
-        <v>6463627</v>
+        <v>6463693</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7181,7 +7180,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7191,7 +7190,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7200,6 +7199,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -6973,10 +6973,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131634080</v>
+        <v>131634505</v>
       </c>
       <c r="B60" t="n">
-        <v>4987</v>
+        <v>93126</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6984,52 +6984,52 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100307</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blompraktbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anthaxia morio</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>560803</v>
+        <v>560686</v>
       </c>
       <c r="R60" t="n">
-        <v>6463627</v>
+        <v>6463693</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7077,6 +7077,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7095,10 +7096,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131634505</v>
+        <v>131634080</v>
       </c>
       <c r="B61" t="n">
-        <v>93126</v>
+        <v>4987</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7106,52 +7107,52 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>100307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blompraktbagge</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthaxia morio</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>560686</v>
+        <v>560803</v>
       </c>
       <c r="R61" t="n">
-        <v>6463693</v>
+        <v>6463627</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7180,7 +7181,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7190,7 +7191,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7199,7 +7200,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -6976,7 +6976,7 @@
         <v>131634080</v>
       </c>
       <c r="B60" t="n">
-        <v>4987</v>
+        <v>4988</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>131634505</v>
       </c>
       <c r="B61" t="n">
-        <v>93126</v>
+        <v>93129</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>131634094</v>
       </c>
       <c r="B62" t="n">
-        <v>101249</v>
+        <v>101252</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>131634130</v>
       </c>
       <c r="B63" t="n">
-        <v>92277</v>
+        <v>92280</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>131633996</v>
       </c>
       <c r="B64" t="n">
-        <v>92262</v>
+        <v>92265</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -7098,7 +7098,7 @@
         <v>131634505</v>
       </c>
       <c r="B61" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>131634094</v>
       </c>
       <c r="B62" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>131634130</v>
       </c>
       <c r="B63" t="n">
-        <v>92280</v>
+        <v>92285</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>131633996</v>
       </c>
       <c r="B64" t="n">
-        <v>92265</v>
+        <v>92270</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -6973,10 +6973,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131634080</v>
+        <v>131634505</v>
       </c>
       <c r="B60" t="n">
-        <v>4988</v>
+        <v>93134</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6984,52 +6984,52 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100307</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blompraktbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anthaxia morio</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>560803</v>
+        <v>560686</v>
       </c>
       <c r="R60" t="n">
-        <v>6463627</v>
+        <v>6463693</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7077,6 +7077,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7095,10 +7096,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131634505</v>
+        <v>131634080</v>
       </c>
       <c r="B61" t="n">
-        <v>93134</v>
+        <v>4988</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7106,52 +7107,52 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>100307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blompraktbagge</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthaxia morio</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>560686</v>
+        <v>560803</v>
       </c>
       <c r="R61" t="n">
-        <v>6463693</v>
+        <v>6463627</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7180,7 +7181,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7190,7 +7191,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7199,7 +7200,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -6976,7 +6976,7 @@
         <v>131634505</v>
       </c>
       <c r="B60" t="n">
-        <v>93134</v>
+        <v>93136</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>131634094</v>
       </c>
       <c r="B62" t="n">
-        <v>101257</v>
+        <v>101260</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>131634130</v>
       </c>
       <c r="B63" t="n">
-        <v>92285</v>
+        <v>92287</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>131633996</v>
       </c>
       <c r="B64" t="n">
-        <v>92270</v>
+        <v>92272</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -6973,10 +6973,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131634505</v>
+        <v>131634080</v>
       </c>
       <c r="B60" t="n">
-        <v>93136</v>
+        <v>4988</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6984,52 +6984,52 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>100307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blompraktbagge</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthaxia morio</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>560686</v>
+        <v>560803</v>
       </c>
       <c r="R60" t="n">
-        <v>6463693</v>
+        <v>6463627</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7077,7 +7077,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7096,10 +7095,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131634080</v>
+        <v>131634505</v>
       </c>
       <c r="B61" t="n">
-        <v>4988</v>
+        <v>93136</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7107,52 +7106,52 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100307</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blompraktbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anthaxia morio</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>560803</v>
+        <v>560686</v>
       </c>
       <c r="R61" t="n">
-        <v>6463627</v>
+        <v>6463693</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7181,7 +7180,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7191,7 +7190,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7200,6 +7199,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -6973,10 +6973,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131634080</v>
+        <v>131634505</v>
       </c>
       <c r="B60" t="n">
-        <v>4988</v>
+        <v>93136</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6984,52 +6984,52 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100307</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blompraktbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anthaxia morio</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>560803</v>
+        <v>560686</v>
       </c>
       <c r="R60" t="n">
-        <v>6463627</v>
+        <v>6463693</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7077,6 +7077,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7095,10 +7096,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131634505</v>
+        <v>131634080</v>
       </c>
       <c r="B61" t="n">
-        <v>93136</v>
+        <v>4988</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7106,52 +7107,52 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>100307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blompraktbagge</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthaxia morio</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Barrskog vid Mulstad, Ög</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>560686</v>
+        <v>560803</v>
       </c>
       <c r="R61" t="n">
-        <v>6463693</v>
+        <v>6463627</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7180,7 +7181,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7190,7 +7191,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7199,7 +7200,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35273-2025 artfynd.xlsx
+++ b/artfynd/A 35273-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AZ93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134111517</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113262</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127354529</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127360190</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127359952</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127359945</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128726511</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1521,6 +1561,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131633996</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1644,6 +1689,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131634505</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1745,6 +1795,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128726409</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1878,6 +1933,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131634064</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1979,6 +2039,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127355314</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2096,6 +2161,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131634130</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2197,6 +2267,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113526</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2298,6 +2373,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127354652</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2399,6 +2479,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127355252</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2500,6 +2585,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127355274</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2601,6 +2691,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127359577</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2702,6 +2797,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127359663</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2803,6 +2903,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127359680</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2909,6 +3014,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127359699</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3010,6 +3120,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127359873</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3111,6 +3226,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127360157</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3212,6 +3332,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127360842</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3313,6 +3438,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128726434</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3423,6 +3553,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128726928</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3524,6 +3659,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128726936</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3625,6 +3765,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134111545</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3726,6 +3871,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113615</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3827,6 +3977,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113638</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3928,6 +4083,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134110911</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4029,6 +4189,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127359655</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4130,6 +4295,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127355375</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4231,6 +4401,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127359702</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4332,6 +4507,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127359854</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4433,6 +4613,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127360466</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4534,6 +4719,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127360616</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4635,6 +4825,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127360687</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4736,6 +4931,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127360839</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4837,6 +5037,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127381942</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4938,6 +5143,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128726497</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5039,6 +5249,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128726518</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5140,6 +5355,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134111527</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5241,6 +5461,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113168</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5342,6 +5567,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113281</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5443,6 +5673,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113641</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5565,6 +5800,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127355148</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5683,6 +5923,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127360121</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5801,6 +6046,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113601</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5914,6 +6164,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127354262</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6032,6 +6287,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127354580</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6150,6 +6410,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127354741</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6272,6 +6537,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127355339</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6390,6 +6660,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127355403</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6508,6 +6783,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127359646</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6626,6 +6906,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127359896</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6743,6 +7028,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127360176</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6865,6 +7155,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127360220</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6983,6 +7278,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127360624</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7101,6 +7401,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127360701</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7214,6 +7519,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127360820</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7332,6 +7642,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127381955</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7450,6 +7765,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127381965</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7572,6 +7892,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127382193</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7682,6 +8007,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128726506</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7792,6 +8122,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128726575</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7897,6 +8232,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128726622</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8019,6 +8359,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128726891</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8136,6 +8481,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131269222</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8258,6 +8608,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134111233</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8363,6 +8718,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134111393</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8468,6 +8828,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134111849</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8586,6 +8951,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113143</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8691,6 +9061,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113557</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8801,6 +9176,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113636</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8919,6 +9299,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113519</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9036,6 +9421,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131269236</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9149,6 +9539,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113348</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9271,6 +9666,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131634080</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9374,6 +9774,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127359706</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9491,6 +9896,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127355369</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9609,6 +10019,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127355188</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9727,6 +10142,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128726475</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9845,6 +10265,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131269217</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9958,6 +10383,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113232</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10061,6 +10491,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113054</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10177,6 +10612,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113001</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10283,6 +10723,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128726614</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10391,6 +10836,11 @@
       <c r="AY90" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874744</t>
         </is>
       </c>
     </row>
@@ -10500,6 +10950,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127354212</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10602,6 +11057,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127355282</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10724,8 +11184,107 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131634094</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>